--- a/selenium-tests/Test_Summary_and_Details_Report.xlsx
+++ b/selenium-tests/Test_Summary_and_Details_Report.xlsx
@@ -5741,7 +5741,7 @@
         <v>52</v>
       </c>
       <c r="I2" s="19">
-        <v>332</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5770,7 +5770,7 @@
         <v>52</v>
       </c>
       <c r="I3" s="19">
-        <v>135</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5799,7 +5799,7 @@
         <v>61</v>
       </c>
       <c r="I4" s="19">
-        <v>515</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5828,7 +5828,7 @@
         <v>52</v>
       </c>
       <c r="I5" s="19">
-        <v>518</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5857,7 +5857,7 @@
         <v>52</v>
       </c>
       <c r="I6" s="19">
-        <v>454</v>
+        <v>517</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5886,7 +5886,7 @@
         <v>61</v>
       </c>
       <c r="I7" s="19">
-        <v>460</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5915,7 +5915,7 @@
         <v>52</v>
       </c>
       <c r="I8" s="19">
-        <v>413</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5944,7 +5944,7 @@
         <v>52</v>
       </c>
       <c r="I9" s="19">
-        <v>301</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5973,7 +5973,7 @@
         <v>61</v>
       </c>
       <c r="I10" s="19">
-        <v>211</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6002,7 +6002,7 @@
         <v>52</v>
       </c>
       <c r="I11" s="19">
-        <v>188</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6031,7 +6031,7 @@
         <v>52</v>
       </c>
       <c r="I12" s="19">
-        <v>260</v>
+        <v>385</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6060,7 +6060,7 @@
         <v>61</v>
       </c>
       <c r="I13" s="19">
-        <v>393</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6089,7 +6089,7 @@
         <v>52</v>
       </c>
       <c r="I14" s="19">
-        <v>429</v>
+        <v>489</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6118,7 +6118,7 @@
         <v>52</v>
       </c>
       <c r="I15" s="19">
-        <v>405</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6147,7 +6147,7 @@
         <v>61</v>
       </c>
       <c r="I16" s="19">
-        <v>502</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6176,7 +6176,7 @@
         <v>52</v>
       </c>
       <c r="I17" s="19">
-        <v>238</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6205,7 +6205,7 @@
         <v>52</v>
       </c>
       <c r="I18" s="19">
-        <v>491</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6234,7 +6234,7 @@
         <v>61</v>
       </c>
       <c r="I19" s="19">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6263,7 +6263,7 @@
         <v>52</v>
       </c>
       <c r="I20" s="19">
-        <v>167</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6292,7 +6292,7 @@
         <v>52</v>
       </c>
       <c r="I21" s="19">
-        <v>314</v>
+        <v>453</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6321,7 +6321,7 @@
         <v>61</v>
       </c>
       <c r="I22" s="19">
-        <v>145</v>
+        <v>419</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6350,7 +6350,7 @@
         <v>52</v>
       </c>
       <c r="I23" s="19">
-        <v>260</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6379,7 +6379,7 @@
         <v>52</v>
       </c>
       <c r="I24" s="19">
-        <v>354</v>
+        <v>449</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6408,7 +6408,7 @@
         <v>61</v>
       </c>
       <c r="I25" s="19">
-        <v>141</v>
+        <v>357</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6437,7 +6437,7 @@
         <v>52</v>
       </c>
       <c r="I26" s="19">
-        <v>122</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6466,7 +6466,7 @@
         <v>52</v>
       </c>
       <c r="I27" s="19">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6495,7 +6495,7 @@
         <v>61</v>
       </c>
       <c r="I28" s="19">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6524,7 +6524,7 @@
         <v>52</v>
       </c>
       <c r="I29" s="19">
-        <v>234</v>
+        <v>465</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6553,7 +6553,7 @@
         <v>52</v>
       </c>
       <c r="I30" s="19">
-        <v>169</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6582,7 +6582,7 @@
         <v>61</v>
       </c>
       <c r="I31" s="19">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6611,7 +6611,7 @@
         <v>52</v>
       </c>
       <c r="I32" s="19">
-        <v>323</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6640,7 +6640,7 @@
         <v>52</v>
       </c>
       <c r="I33" s="19">
-        <v>298</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6669,7 +6669,7 @@
         <v>61</v>
       </c>
       <c r="I34" s="19">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6698,7 +6698,7 @@
         <v>52</v>
       </c>
       <c r="I35" s="19">
-        <v>397</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6727,7 +6727,7 @@
         <v>52</v>
       </c>
       <c r="I36" s="19">
-        <v>378</v>
+        <v>393</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6756,7 +6756,7 @@
         <v>61</v>
       </c>
       <c r="I37" s="19">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6785,7 +6785,7 @@
         <v>52</v>
       </c>
       <c r="I38" s="19">
-        <v>507</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6814,7 +6814,7 @@
         <v>52</v>
       </c>
       <c r="I39" s="19">
-        <v>402</v>
+        <v>271</v>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6843,7 +6843,7 @@
         <v>61</v>
       </c>
       <c r="I40" s="19">
-        <v>217</v>
+        <v>352</v>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6872,7 +6872,7 @@
         <v>52</v>
       </c>
       <c r="I41" s="19">
-        <v>294</v>
+        <v>485</v>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6901,7 +6901,7 @@
         <v>52</v>
       </c>
       <c r="I42" s="19">
-        <v>445</v>
+        <v>181</v>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6930,7 +6930,7 @@
         <v>61</v>
       </c>
       <c r="I43" s="19">
-        <v>314</v>
+        <v>393</v>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6959,7 +6959,7 @@
         <v>52</v>
       </c>
       <c r="I44" s="19">
-        <v>204</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6988,7 +6988,7 @@
         <v>52</v>
       </c>
       <c r="I45" s="19">
-        <v>216</v>
+        <v>289</v>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7017,7 +7017,7 @@
         <v>61</v>
       </c>
       <c r="I46" s="19">
-        <v>246</v>
+        <v>489</v>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7046,7 +7046,7 @@
         <v>52</v>
       </c>
       <c r="I47" s="19">
-        <v>273</v>
+        <v>496</v>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7075,7 +7075,7 @@
         <v>52</v>
       </c>
       <c r="I48" s="19">
-        <v>254</v>
+        <v>363</v>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7104,7 +7104,7 @@
         <v>61</v>
       </c>
       <c r="I49" s="19">
-        <v>457</v>
+        <v>426</v>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7133,7 +7133,7 @@
         <v>52</v>
       </c>
       <c r="I50" s="19">
-        <v>425</v>
+        <v>497</v>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7162,7 +7162,7 @@
         <v>52</v>
       </c>
       <c r="I51" s="19">
-        <v>498</v>
+        <v>394</v>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7191,7 +7191,7 @@
         <v>61</v>
       </c>
       <c r="I52" s="19">
-        <v>243</v>
+        <v>195</v>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7220,7 +7220,7 @@
         <v>52</v>
       </c>
       <c r="I53" s="19">
-        <v>293</v>
+        <v>327</v>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7249,7 +7249,7 @@
         <v>52</v>
       </c>
       <c r="I54" s="19">
-        <v>276</v>
+        <v>479</v>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7278,7 +7278,7 @@
         <v>61</v>
       </c>
       <c r="I55" s="19">
-        <v>455</v>
+        <v>384</v>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7307,7 +7307,7 @@
         <v>273</v>
       </c>
       <c r="I56" s="19">
-        <v>255</v>
+        <v>440</v>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7336,7 +7336,7 @@
         <v>52</v>
       </c>
       <c r="I57" s="19">
-        <v>453</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7365,7 +7365,7 @@
         <v>61</v>
       </c>
       <c r="I58" s="19">
-        <v>232</v>
+        <v>372</v>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7394,7 +7394,7 @@
         <v>52</v>
       </c>
       <c r="I59" s="19">
-        <v>403</v>
+        <v>249</v>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7423,7 +7423,7 @@
         <v>52</v>
       </c>
       <c r="I60" s="19">
-        <v>509</v>
+        <v>430</v>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7452,7 +7452,7 @@
         <v>61</v>
       </c>
       <c r="I61" s="19">
-        <v>199</v>
+        <v>500</v>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7481,7 +7481,7 @@
         <v>52</v>
       </c>
       <c r="I62" s="19">
-        <v>415</v>
+        <v>311</v>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7510,7 +7510,7 @@
         <v>52</v>
       </c>
       <c r="I63" s="19">
-        <v>139</v>
+        <v>428</v>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7539,7 +7539,7 @@
         <v>61</v>
       </c>
       <c r="I64" s="19">
-        <v>152</v>
+        <v>351</v>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7568,7 +7568,7 @@
         <v>52</v>
       </c>
       <c r="I65" s="19">
-        <v>357</v>
+        <v>129</v>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7597,7 +7597,7 @@
         <v>52</v>
       </c>
       <c r="I66" s="19">
-        <v>451</v>
+        <v>162</v>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7626,7 +7626,7 @@
         <v>61</v>
       </c>
       <c r="I67" s="19">
-        <v>432</v>
+        <v>141</v>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7655,7 +7655,7 @@
         <v>52</v>
       </c>
       <c r="I68" s="19">
-        <v>271</v>
+        <v>374</v>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7684,7 +7684,7 @@
         <v>52</v>
       </c>
       <c r="I69" s="19">
-        <v>254</v>
+        <v>178</v>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7713,7 +7713,7 @@
         <v>61</v>
       </c>
       <c r="I70" s="19">
-        <v>372</v>
+        <v>476</v>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7742,7 +7742,7 @@
         <v>52</v>
       </c>
       <c r="I71" s="19">
-        <v>146</v>
+        <v>411</v>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7771,7 +7771,7 @@
         <v>52</v>
       </c>
       <c r="I72" s="19">
-        <v>467</v>
+        <v>171</v>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7800,7 +7800,7 @@
         <v>61</v>
       </c>
       <c r="I73" s="19">
-        <v>214</v>
+        <v>456</v>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7829,7 +7829,7 @@
         <v>52</v>
       </c>
       <c r="I74" s="19">
-        <v>440</v>
+        <v>306</v>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7858,7 +7858,7 @@
         <v>52</v>
       </c>
       <c r="I75" s="19">
-        <v>403</v>
+        <v>465</v>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7887,7 +7887,7 @@
         <v>61</v>
       </c>
       <c r="I76" s="19">
-        <v>167</v>
+        <v>367</v>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7916,7 +7916,7 @@
         <v>52</v>
       </c>
       <c r="I77" s="19">
-        <v>168</v>
+        <v>482</v>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7945,7 +7945,7 @@
         <v>52</v>
       </c>
       <c r="I78" s="19">
-        <v>382</v>
+        <v>458</v>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7974,7 +7974,7 @@
         <v>61</v>
       </c>
       <c r="I79" s="19">
-        <v>152</v>
+        <v>406</v>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8003,7 +8003,7 @@
         <v>52</v>
       </c>
       <c r="I80" s="19">
-        <v>255</v>
+        <v>426</v>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8032,7 +8032,7 @@
         <v>52</v>
       </c>
       <c r="I81" s="19">
-        <v>157</v>
+        <v>386</v>
       </c>
     </row>
     <row r="82" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8061,7 +8061,7 @@
         <v>61</v>
       </c>
       <c r="I82" s="19">
-        <v>485</v>
+        <v>191</v>
       </c>
     </row>
     <row r="83" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8090,7 +8090,7 @@
         <v>52</v>
       </c>
       <c r="I83" s="19">
-        <v>264</v>
+        <v>507</v>
       </c>
     </row>
     <row r="84" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8119,7 +8119,7 @@
         <v>52</v>
       </c>
       <c r="I84" s="19">
-        <v>210</v>
+        <v>128</v>
       </c>
     </row>
     <row r="85" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8148,7 +8148,7 @@
         <v>61</v>
       </c>
       <c r="I85" s="19">
-        <v>133</v>
+        <v>249</v>
       </c>
     </row>
     <row r="86" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8177,7 +8177,7 @@
         <v>52</v>
       </c>
       <c r="I86" s="19">
-        <v>287</v>
+        <v>272</v>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8206,7 +8206,7 @@
         <v>52</v>
       </c>
       <c r="I87" s="19">
-        <v>318</v>
+        <v>419</v>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8235,7 +8235,7 @@
         <v>61</v>
       </c>
       <c r="I88" s="19">
-        <v>244</v>
+        <v>281</v>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8264,7 +8264,7 @@
         <v>52</v>
       </c>
       <c r="I89" s="19">
-        <v>172</v>
+        <v>307</v>
       </c>
     </row>
     <row r="90" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8293,7 +8293,7 @@
         <v>52</v>
       </c>
       <c r="I90" s="19">
-        <v>355</v>
+        <v>305</v>
       </c>
     </row>
     <row r="91" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8322,7 +8322,7 @@
         <v>61</v>
       </c>
       <c r="I91" s="19">
-        <v>140</v>
+        <v>345</v>
       </c>
     </row>
     <row r="92" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8351,7 +8351,7 @@
         <v>52</v>
       </c>
       <c r="I92" s="19">
-        <v>416</v>
+        <v>410</v>
       </c>
     </row>
     <row r="93" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8380,7 +8380,7 @@
         <v>52</v>
       </c>
       <c r="I93" s="19">
-        <v>371</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8409,7 +8409,7 @@
         <v>61</v>
       </c>
       <c r="I94" s="19">
-        <v>176</v>
+        <v>329</v>
       </c>
     </row>
     <row r="95" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8438,7 +8438,7 @@
         <v>52</v>
       </c>
       <c r="I95" s="19">
-        <v>259</v>
+        <v>348</v>
       </c>
     </row>
     <row r="96" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8467,7 +8467,7 @@
         <v>52</v>
       </c>
       <c r="I96" s="19">
-        <v>339</v>
+        <v>268</v>
       </c>
     </row>
     <row r="97" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8496,7 +8496,7 @@
         <v>61</v>
       </c>
       <c r="I97" s="19">
-        <v>207</v>
+        <v>221</v>
       </c>
     </row>
     <row r="98" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8525,7 +8525,7 @@
         <v>52</v>
       </c>
       <c r="I98" s="19">
-        <v>364</v>
+        <v>447</v>
       </c>
     </row>
     <row r="99" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8554,7 +8554,7 @@
         <v>52</v>
       </c>
       <c r="I99" s="19">
-        <v>378</v>
+        <v>140</v>
       </c>
     </row>
     <row r="100" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8583,7 +8583,7 @@
         <v>61</v>
       </c>
       <c r="I100" s="19">
-        <v>137</v>
+        <v>420</v>
       </c>
     </row>
     <row r="101" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8612,7 +8612,7 @@
         <v>52</v>
       </c>
       <c r="I101" s="19">
-        <v>503</v>
+        <v>265</v>
       </c>
     </row>
     <row r="102" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8641,7 +8641,7 @@
         <v>52</v>
       </c>
       <c r="I102" s="19">
-        <v>325</v>
+        <v>314</v>
       </c>
     </row>
     <row r="103" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8670,7 +8670,7 @@
         <v>61</v>
       </c>
       <c r="I103" s="19">
-        <v>314</v>
+        <v>402</v>
       </c>
     </row>
     <row r="104" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8699,7 +8699,7 @@
         <v>52</v>
       </c>
       <c r="I104" s="19">
-        <v>220</v>
+        <v>396</v>
       </c>
     </row>
     <row r="105" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8728,7 +8728,7 @@
         <v>52</v>
       </c>
       <c r="I105" s="19">
-        <v>411</v>
+        <v>458</v>
       </c>
     </row>
     <row r="106" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8757,7 +8757,7 @@
         <v>61</v>
       </c>
       <c r="I106" s="19">
-        <v>444</v>
+        <v>249</v>
       </c>
     </row>
     <row r="107" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8786,7 +8786,7 @@
         <v>52</v>
       </c>
       <c r="I107" s="19">
-        <v>177</v>
+        <v>328</v>
       </c>
     </row>
     <row r="108" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8815,7 +8815,7 @@
         <v>52</v>
       </c>
       <c r="I108" s="19">
-        <v>333</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8844,7 +8844,7 @@
         <v>61</v>
       </c>
       <c r="I109" s="19">
-        <v>458</v>
+        <v>195</v>
       </c>
     </row>
     <row r="110" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8873,7 +8873,7 @@
         <v>52</v>
       </c>
       <c r="I110" s="19">
-        <v>313</v>
+        <v>152</v>
       </c>
     </row>
     <row r="111" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8902,7 +8902,7 @@
         <v>273</v>
       </c>
       <c r="I111" s="19">
-        <v>351</v>
+        <v>220</v>
       </c>
     </row>
     <row r="112" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8931,7 +8931,7 @@
         <v>61</v>
       </c>
       <c r="I112" s="19">
-        <v>273</v>
+        <v>312</v>
       </c>
     </row>
     <row r="113" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8960,7 +8960,7 @@
         <v>52</v>
       </c>
       <c r="I113" s="19">
-        <v>135</v>
+        <v>328</v>
       </c>
     </row>
     <row r="114" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8989,7 +8989,7 @@
         <v>52</v>
       </c>
       <c r="I114" s="19">
-        <v>149</v>
+        <v>365</v>
       </c>
     </row>
     <row r="115" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9018,7 +9018,7 @@
         <v>61</v>
       </c>
       <c r="I115" s="19">
-        <v>189</v>
+        <v>463</v>
       </c>
     </row>
     <row r="116" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9047,7 +9047,7 @@
         <v>52</v>
       </c>
       <c r="I116" s="19">
-        <v>281</v>
+        <v>130</v>
       </c>
     </row>
     <row r="117" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9076,7 +9076,7 @@
         <v>52</v>
       </c>
       <c r="I117" s="19">
-        <v>291</v>
+        <v>153</v>
       </c>
     </row>
     <row r="118" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9105,7 +9105,7 @@
         <v>61</v>
       </c>
       <c r="I118" s="19">
-        <v>305</v>
+        <v>348</v>
       </c>
     </row>
     <row r="119" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9134,7 +9134,7 @@
         <v>52</v>
       </c>
       <c r="I119" s="19">
-        <v>408</v>
+        <v>270</v>
       </c>
     </row>
     <row r="120" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9163,7 +9163,7 @@
         <v>52</v>
       </c>
       <c r="I120" s="19">
-        <v>333</v>
+        <v>477</v>
       </c>
     </row>
     <row r="121" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9192,7 +9192,7 @@
         <v>61</v>
       </c>
       <c r="I121" s="19">
-        <v>219</v>
+        <v>332</v>
       </c>
     </row>
     <row r="122" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9221,7 +9221,7 @@
         <v>52</v>
       </c>
       <c r="I122" s="19">
-        <v>402</v>
+        <v>434</v>
       </c>
     </row>
     <row r="123" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9250,7 +9250,7 @@
         <v>52</v>
       </c>
       <c r="I123" s="19">
-        <v>455</v>
+        <v>343</v>
       </c>
     </row>
     <row r="124" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9279,7 +9279,7 @@
         <v>61</v>
       </c>
       <c r="I124" s="19">
-        <v>212</v>
+        <v>433</v>
       </c>
     </row>
     <row r="125" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9308,7 +9308,7 @@
         <v>52</v>
       </c>
       <c r="I125" s="19">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="126" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9337,7 +9337,7 @@
         <v>52</v>
       </c>
       <c r="I126" s="19">
-        <v>195</v>
+        <v>397</v>
       </c>
     </row>
     <row r="127" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9366,7 +9366,7 @@
         <v>61</v>
       </c>
       <c r="I127" s="19">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="128" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9395,7 +9395,7 @@
         <v>52</v>
       </c>
       <c r="I128" s="19">
-        <v>152</v>
+        <v>202</v>
       </c>
     </row>
     <row r="129" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9424,7 +9424,7 @@
         <v>52</v>
       </c>
       <c r="I129" s="19">
-        <v>309</v>
+        <v>375</v>
       </c>
     </row>
     <row r="130" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9453,7 +9453,7 @@
         <v>61</v>
       </c>
       <c r="I130" s="19">
-        <v>317</v>
+        <v>339</v>
       </c>
     </row>
     <row r="131" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9482,7 +9482,7 @@
         <v>52</v>
       </c>
       <c r="I131" s="19">
-        <v>214</v>
+        <v>289</v>
       </c>
     </row>
     <row r="132" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9511,7 +9511,7 @@
         <v>52</v>
       </c>
       <c r="I132" s="19">
-        <v>279</v>
+        <v>501</v>
       </c>
     </row>
     <row r="133" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9540,7 +9540,7 @@
         <v>61</v>
       </c>
       <c r="I133" s="19">
-        <v>184</v>
+        <v>407</v>
       </c>
     </row>
     <row r="134" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9569,7 +9569,7 @@
         <v>52</v>
       </c>
       <c r="I134" s="19">
-        <v>478</v>
+        <v>432</v>
       </c>
     </row>
     <row r="135" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9598,7 +9598,7 @@
         <v>52</v>
       </c>
       <c r="I135" s="19">
-        <v>309</v>
+        <v>144</v>
       </c>
     </row>
     <row r="136" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9627,7 +9627,7 @@
         <v>61</v>
       </c>
       <c r="I136" s="19">
-        <v>311</v>
+        <v>199</v>
       </c>
     </row>
     <row r="137" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9656,7 +9656,7 @@
         <v>52</v>
       </c>
       <c r="I137" s="19">
-        <v>290</v>
+        <v>357</v>
       </c>
     </row>
     <row r="138" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9685,7 +9685,7 @@
         <v>52</v>
       </c>
       <c r="I138" s="19">
-        <v>279</v>
+        <v>236</v>
       </c>
     </row>
     <row r="139" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9714,7 +9714,7 @@
         <v>61</v>
       </c>
       <c r="I139" s="19">
-        <v>187</v>
+        <v>420</v>
       </c>
     </row>
     <row r="140" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9743,7 +9743,7 @@
         <v>52</v>
       </c>
       <c r="I140" s="19">
-        <v>135</v>
+        <v>228</v>
       </c>
     </row>
     <row r="141" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9772,7 +9772,7 @@
         <v>52</v>
       </c>
       <c r="I141" s="19">
-        <v>157</v>
+        <v>255</v>
       </c>
     </row>
     <row r="142" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9801,7 +9801,7 @@
         <v>61</v>
       </c>
       <c r="I142" s="19">
-        <v>489</v>
+        <v>328</v>
       </c>
     </row>
     <row r="143" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9830,7 +9830,7 @@
         <v>52</v>
       </c>
       <c r="I143" s="19">
-        <v>128</v>
+        <v>253</v>
       </c>
     </row>
     <row r="144" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9859,7 +9859,7 @@
         <v>52</v>
       </c>
       <c r="I144" s="19">
-        <v>231</v>
+        <v>378</v>
       </c>
     </row>
     <row r="145" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9888,7 +9888,7 @@
         <v>61</v>
       </c>
       <c r="I145" s="19">
-        <v>286</v>
+        <v>158</v>
       </c>
     </row>
     <row r="146" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9917,7 +9917,7 @@
         <v>52</v>
       </c>
       <c r="I146" s="19">
-        <v>432</v>
+        <v>183</v>
       </c>
     </row>
     <row r="147" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9946,7 +9946,7 @@
         <v>52</v>
       </c>
       <c r="I147" s="19">
-        <v>499</v>
+        <v>341</v>
       </c>
     </row>
     <row r="148" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9975,7 +9975,7 @@
         <v>61</v>
       </c>
       <c r="I148" s="19">
-        <v>226</v>
+        <v>155</v>
       </c>
     </row>
     <row r="149" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10004,7 +10004,7 @@
         <v>52</v>
       </c>
       <c r="I149" s="19">
-        <v>428</v>
+        <v>303</v>
       </c>
     </row>
     <row r="150" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10033,7 +10033,7 @@
         <v>52</v>
       </c>
       <c r="I150" s="19">
-        <v>251</v>
+        <v>183</v>
       </c>
     </row>
     <row r="151" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10062,7 +10062,7 @@
         <v>61</v>
       </c>
       <c r="I151" s="19">
-        <v>167</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10091,7 +10091,7 @@
         <v>52</v>
       </c>
       <c r="I152" s="19">
-        <v>404</v>
+        <v>168</v>
       </c>
     </row>
     <row r="153" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10120,7 +10120,7 @@
         <v>52</v>
       </c>
       <c r="I153" s="19">
-        <v>214</v>
+        <v>496</v>
       </c>
     </row>
     <row r="154" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10149,7 +10149,7 @@
         <v>61</v>
       </c>
       <c r="I154" s="19">
-        <v>418</v>
+        <v>285</v>
       </c>
     </row>
     <row r="155" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10178,7 +10178,7 @@
         <v>52</v>
       </c>
       <c r="I155" s="19">
-        <v>376</v>
+        <v>146</v>
       </c>
     </row>
     <row r="156" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10207,7 +10207,7 @@
         <v>52</v>
       </c>
       <c r="I156" s="19">
-        <v>419</v>
+        <v>236</v>
       </c>
     </row>
     <row r="157" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10236,7 +10236,7 @@
         <v>61</v>
       </c>
       <c r="I157" s="19">
-        <v>121</v>
+        <v>389</v>
       </c>
     </row>
     <row r="158" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10265,7 +10265,7 @@
         <v>52</v>
       </c>
       <c r="I158" s="19">
-        <v>329</v>
+        <v>350</v>
       </c>
     </row>
     <row r="159" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10294,7 +10294,7 @@
         <v>52</v>
       </c>
       <c r="I159" s="19">
-        <v>270</v>
+        <v>377</v>
       </c>
     </row>
     <row r="160" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10323,7 +10323,7 @@
         <v>61</v>
       </c>
       <c r="I160" s="19">
-        <v>493</v>
+        <v>144</v>
       </c>
     </row>
     <row r="161" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10352,7 +10352,7 @@
         <v>52</v>
       </c>
       <c r="I161" s="19">
-        <v>248</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10381,7 +10381,7 @@
         <v>52</v>
       </c>
       <c r="I162" s="19">
-        <v>511</v>
+        <v>501</v>
       </c>
     </row>
     <row r="163" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10410,7 +10410,7 @@
         <v>61</v>
       </c>
       <c r="I163" s="19">
-        <v>216</v>
+        <v>311</v>
       </c>
     </row>
     <row r="164" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10439,7 +10439,7 @@
         <v>52</v>
       </c>
       <c r="I164" s="19">
-        <v>285</v>
+        <v>321</v>
       </c>
     </row>
     <row r="165" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10468,7 +10468,7 @@
         <v>52</v>
       </c>
       <c r="I165" s="19">
-        <v>230</v>
+        <v>340</v>
       </c>
     </row>
     <row r="166" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10497,7 +10497,7 @@
         <v>273</v>
       </c>
       <c r="I166" s="19">
-        <v>285</v>
+        <v>364</v>
       </c>
     </row>
     <row r="167" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10526,7 +10526,7 @@
         <v>52</v>
       </c>
       <c r="I167" s="19">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="168" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10555,7 +10555,7 @@
         <v>52</v>
       </c>
       <c r="I168" s="19">
-        <v>313</v>
+        <v>167</v>
       </c>
     </row>
     <row r="169" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10584,7 +10584,7 @@
         <v>61</v>
       </c>
       <c r="I169" s="19">
-        <v>158</v>
+        <v>398</v>
       </c>
     </row>
     <row r="170" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10613,7 +10613,7 @@
         <v>52</v>
       </c>
       <c r="I170" s="19">
-        <v>151</v>
+        <v>349</v>
       </c>
     </row>
     <row r="171" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10642,7 +10642,7 @@
         <v>52</v>
       </c>
       <c r="I171" s="19">
-        <v>355</v>
+        <v>157</v>
       </c>
     </row>
     <row r="172" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10671,7 +10671,7 @@
         <v>61</v>
       </c>
       <c r="I172" s="19">
-        <v>268</v>
+        <v>350</v>
       </c>
     </row>
     <row r="173" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10700,7 +10700,7 @@
         <v>52</v>
       </c>
       <c r="I173" s="19">
-        <v>487</v>
+        <v>167</v>
       </c>
     </row>
     <row r="174" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10729,7 +10729,7 @@
         <v>52</v>
       </c>
       <c r="I174" s="19">
-        <v>304</v>
+        <v>268</v>
       </c>
     </row>
     <row r="175" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10758,7 +10758,7 @@
         <v>61</v>
       </c>
       <c r="I175" s="19">
-        <v>122</v>
+        <v>396</v>
       </c>
     </row>
     <row r="176" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10787,7 +10787,7 @@
         <v>52</v>
       </c>
       <c r="I176" s="19">
-        <v>176</v>
+        <v>390</v>
       </c>
     </row>
     <row r="177" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10816,7 +10816,7 @@
         <v>52</v>
       </c>
       <c r="I177" s="19">
-        <v>443</v>
+        <v>455</v>
       </c>
     </row>
     <row r="178" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10845,7 +10845,7 @@
         <v>61</v>
       </c>
       <c r="I178" s="19">
-        <v>328</v>
+        <v>122</v>
       </c>
     </row>
     <row r="179" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10874,7 +10874,7 @@
         <v>52</v>
       </c>
       <c r="I179" s="19">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="180" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10903,7 +10903,7 @@
         <v>52</v>
       </c>
       <c r="I180" s="19">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="181" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10932,7 +10932,7 @@
         <v>61</v>
       </c>
       <c r="I181" s="19">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="182" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10961,7 +10961,7 @@
         <v>52</v>
       </c>
       <c r="I182" s="19">
-        <v>295</v>
+        <v>120</v>
       </c>
     </row>
     <row r="183" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10990,7 +10990,7 @@
         <v>52</v>
       </c>
       <c r="I183" s="19">
-        <v>506</v>
+        <v>464</v>
       </c>
     </row>
     <row r="184" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11019,7 +11019,7 @@
         <v>61</v>
       </c>
       <c r="I184" s="19">
-        <v>425</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11048,7 +11048,7 @@
         <v>52</v>
       </c>
       <c r="I185" s="19">
-        <v>446</v>
+        <v>182</v>
       </c>
     </row>
     <row r="186" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11077,7 +11077,7 @@
         <v>52</v>
       </c>
       <c r="I186" s="19">
-        <v>458</v>
+        <v>434</v>
       </c>
     </row>
     <row r="187" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11106,7 +11106,7 @@
         <v>61</v>
       </c>
       <c r="I187" s="19">
-        <v>277</v>
+        <v>389</v>
       </c>
     </row>
     <row r="188" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11135,7 +11135,7 @@
         <v>52</v>
       </c>
       <c r="I188" s="19">
-        <v>479</v>
+        <v>462</v>
       </c>
     </row>
     <row r="189" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11164,7 +11164,7 @@
         <v>52</v>
       </c>
       <c r="I189" s="19">
-        <v>315</v>
+        <v>346</v>
       </c>
     </row>
     <row r="190" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11193,7 +11193,7 @@
         <v>61</v>
       </c>
       <c r="I190" s="19">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="191" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11222,7 +11222,7 @@
         <v>52</v>
       </c>
       <c r="I191" s="19">
-        <v>287</v>
+        <v>433</v>
       </c>
     </row>
     <row r="192" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11251,7 +11251,7 @@
         <v>52</v>
       </c>
       <c r="I192" s="19">
-        <v>308</v>
+        <v>124</v>
       </c>
     </row>
     <row r="193" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11280,7 +11280,7 @@
         <v>61</v>
       </c>
       <c r="I193" s="19">
-        <v>189</v>
+        <v>228</v>
       </c>
     </row>
     <row r="194" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11309,7 +11309,7 @@
         <v>52</v>
       </c>
       <c r="I194" s="19">
-        <v>304</v>
+        <v>231</v>
       </c>
     </row>
     <row r="195" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11338,7 +11338,7 @@
         <v>52</v>
       </c>
       <c r="I195" s="19">
-        <v>287</v>
+        <v>132</v>
       </c>
     </row>
     <row r="196" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11367,7 +11367,7 @@
         <v>61</v>
       </c>
       <c r="I196" s="19">
-        <v>424</v>
+        <v>456</v>
       </c>
     </row>
     <row r="197" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11396,7 +11396,7 @@
         <v>52</v>
       </c>
       <c r="I197" s="19">
-        <v>461</v>
+        <v>172</v>
       </c>
     </row>
     <row r="198" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11425,7 +11425,7 @@
         <v>52</v>
       </c>
       <c r="I198" s="19">
-        <v>291</v>
+        <v>265</v>
       </c>
     </row>
     <row r="199" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11454,7 +11454,7 @@
         <v>61</v>
       </c>
       <c r="I199" s="19">
-        <v>515</v>
+        <v>165</v>
       </c>
     </row>
     <row r="200" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11483,7 +11483,7 @@
         <v>52</v>
       </c>
       <c r="I200" s="19">
-        <v>146</v>
+        <v>328</v>
       </c>
     </row>
     <row r="201" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11512,7 +11512,7 @@
         <v>52</v>
       </c>
       <c r="I201" s="19">
-        <v>238</v>
+        <v>223</v>
       </c>
     </row>
     <row r="202" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11541,7 +11541,7 @@
         <v>61</v>
       </c>
       <c r="I202" s="19">
-        <v>413</v>
+        <v>483</v>
       </c>
     </row>
     <row r="203" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11570,7 +11570,7 @@
         <v>52</v>
       </c>
       <c r="I203" s="19">
-        <v>135</v>
+        <v>122</v>
       </c>
     </row>
     <row r="204" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11599,7 +11599,7 @@
         <v>52</v>
       </c>
       <c r="I204" s="19">
-        <v>300</v>
+        <v>407</v>
       </c>
     </row>
     <row r="205" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11628,7 +11628,7 @@
         <v>61</v>
       </c>
       <c r="I205" s="19">
-        <v>287</v>
+        <v>143</v>
       </c>
     </row>
     <row r="206" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11657,7 +11657,7 @@
         <v>52</v>
       </c>
       <c r="I206" s="19">
-        <v>130</v>
+        <v>451</v>
       </c>
     </row>
     <row r="207" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11686,7 +11686,7 @@
         <v>52</v>
       </c>
       <c r="I207" s="19">
-        <v>164</v>
+        <v>462</v>
       </c>
     </row>
     <row r="208" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11715,7 +11715,7 @@
         <v>61</v>
       </c>
       <c r="I208" s="19">
-        <v>501</v>
+        <v>252</v>
       </c>
     </row>
     <row r="209" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11744,7 +11744,7 @@
         <v>52</v>
       </c>
       <c r="I209" s="19">
-        <v>390</v>
+        <v>235</v>
       </c>
     </row>
     <row r="210" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11773,7 +11773,7 @@
         <v>52</v>
       </c>
       <c r="I210" s="19">
-        <v>344</v>
+        <v>294</v>
       </c>
     </row>
     <row r="211" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11802,7 +11802,7 @@
         <v>61</v>
       </c>
       <c r="I211" s="19">
-        <v>188</v>
+        <v>431</v>
       </c>
     </row>
     <row r="212" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11831,7 +11831,7 @@
         <v>52</v>
       </c>
       <c r="I212" s="19">
-        <v>491</v>
+        <v>468</v>
       </c>
     </row>
     <row r="213" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11860,7 +11860,7 @@
         <v>52</v>
       </c>
       <c r="I213" s="19">
-        <v>141</v>
+        <v>432</v>
       </c>
     </row>
     <row r="214" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11889,7 +11889,7 @@
         <v>61</v>
       </c>
       <c r="I214" s="19">
-        <v>477</v>
+        <v>313</v>
       </c>
     </row>
     <row r="215" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11918,7 +11918,7 @@
         <v>52</v>
       </c>
       <c r="I215" s="19">
-        <v>516</v>
+        <v>371</v>
       </c>
     </row>
     <row r="216" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11947,7 +11947,7 @@
         <v>52</v>
       </c>
       <c r="I216" s="19">
-        <v>203</v>
+        <v>334</v>
       </c>
     </row>
     <row r="217" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11976,7 +11976,7 @@
         <v>61</v>
       </c>
       <c r="I217" s="19">
-        <v>293</v>
+        <v>349</v>
       </c>
     </row>
     <row r="218" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12005,7 +12005,7 @@
         <v>52</v>
       </c>
       <c r="I218" s="19">
-        <v>475</v>
+        <v>190</v>
       </c>
     </row>
     <row r="219" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12034,7 +12034,7 @@
         <v>52</v>
       </c>
       <c r="I219" s="19">
-        <v>216</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12063,7 +12063,7 @@
         <v>61</v>
       </c>
       <c r="I220" s="19">
-        <v>196</v>
+        <v>461</v>
       </c>
     </row>
     <row r="221" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12092,7 +12092,7 @@
         <v>273</v>
       </c>
       <c r="I221" s="19">
-        <v>144</v>
+        <v>317</v>
       </c>
     </row>
     <row r="222" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12121,7 +12121,7 @@
         <v>52</v>
       </c>
       <c r="I222" s="19">
-        <v>289</v>
+        <v>179</v>
       </c>
     </row>
     <row r="223" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12150,7 +12150,7 @@
         <v>61</v>
       </c>
       <c r="I223" s="19">
-        <v>415</v>
+        <v>217</v>
       </c>
     </row>
     <row r="224" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12179,7 +12179,7 @@
         <v>52</v>
       </c>
       <c r="I224" s="19">
-        <v>322</v>
+        <v>245</v>
       </c>
     </row>
     <row r="225" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12208,7 +12208,7 @@
         <v>52</v>
       </c>
       <c r="I225" s="19">
-        <v>516</v>
+        <v>255</v>
       </c>
     </row>
     <row r="226" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12237,7 +12237,7 @@
         <v>61</v>
       </c>
       <c r="I226" s="19">
-        <v>147</v>
+        <v>175</v>
       </c>
     </row>
     <row r="227" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12266,7 +12266,7 @@
         <v>52</v>
       </c>
       <c r="I227" s="19">
-        <v>214</v>
+        <v>155</v>
       </c>
     </row>
     <row r="228" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12295,7 +12295,7 @@
         <v>52</v>
       </c>
       <c r="I228" s="19">
-        <v>401</v>
+        <v>470</v>
       </c>
     </row>
     <row r="229" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12324,7 +12324,7 @@
         <v>61</v>
       </c>
       <c r="I229" s="19">
-        <v>393</v>
+        <v>373</v>
       </c>
     </row>
     <row r="230" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12353,7 +12353,7 @@
         <v>52</v>
       </c>
       <c r="I230" s="19">
-        <v>428</v>
+        <v>123</v>
       </c>
     </row>
     <row r="231" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12382,7 +12382,7 @@
         <v>52</v>
       </c>
       <c r="I231" s="19">
-        <v>199</v>
+        <v>304</v>
       </c>
     </row>
     <row r="232" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12411,7 +12411,7 @@
         <v>61</v>
       </c>
       <c r="I232" s="19">
-        <v>143</v>
+        <v>207</v>
       </c>
     </row>
     <row r="233" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12440,7 +12440,7 @@
         <v>52</v>
       </c>
       <c r="I233" s="19">
-        <v>128</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12469,7 +12469,7 @@
         <v>52</v>
       </c>
       <c r="I234" s="19">
-        <v>456</v>
+        <v>280</v>
       </c>
     </row>
     <row r="235" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12498,7 +12498,7 @@
         <v>61</v>
       </c>
       <c r="I235" s="19">
-        <v>330</v>
+        <v>317</v>
       </c>
     </row>
     <row r="236" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12527,7 +12527,7 @@
         <v>52</v>
       </c>
       <c r="I236" s="19">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="237" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12556,7 +12556,7 @@
         <v>52</v>
       </c>
       <c r="I237" s="19">
-        <v>147</v>
+        <v>447</v>
       </c>
     </row>
     <row r="238" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12585,7 +12585,7 @@
         <v>61</v>
       </c>
       <c r="I238" s="19">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="239" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12614,7 +12614,7 @@
         <v>52</v>
       </c>
       <c r="I239" s="19">
-        <v>365</v>
+        <v>131</v>
       </c>
     </row>
     <row r="240" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12643,7 +12643,7 @@
         <v>52</v>
       </c>
       <c r="I240" s="19">
-        <v>314</v>
+        <v>337</v>
       </c>
     </row>
     <row r="241" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12672,7 +12672,7 @@
         <v>61</v>
       </c>
       <c r="I241" s="19">
-        <v>453</v>
+        <v>427</v>
       </c>
     </row>
     <row r="242" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12701,7 +12701,7 @@
         <v>52</v>
       </c>
       <c r="I242" s="19">
-        <v>454</v>
+        <v>368</v>
       </c>
     </row>
     <row r="243" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12730,7 +12730,7 @@
         <v>52</v>
       </c>
       <c r="I243" s="19">
-        <v>333</v>
+        <v>252</v>
       </c>
     </row>
     <row r="244" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12759,7 +12759,7 @@
         <v>61</v>
       </c>
       <c r="I244" s="19">
-        <v>502</v>
+        <v>147</v>
       </c>
     </row>
     <row r="245" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12788,7 +12788,7 @@
         <v>52</v>
       </c>
       <c r="I245" s="19">
-        <v>474</v>
+        <v>218</v>
       </c>
     </row>
     <row r="246" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12817,7 +12817,7 @@
         <v>52</v>
       </c>
       <c r="I246" s="19">
-        <v>206</v>
+        <v>471</v>
       </c>
     </row>
     <row r="247" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12846,7 +12846,7 @@
         <v>61</v>
       </c>
       <c r="I247" s="19">
-        <v>360</v>
+        <v>345</v>
       </c>
     </row>
     <row r="248" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12875,7 +12875,7 @@
         <v>52</v>
       </c>
       <c r="I248" s="19">
-        <v>288</v>
+        <v>406</v>
       </c>
     </row>
     <row r="249" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12904,7 +12904,7 @@
         <v>52</v>
       </c>
       <c r="I249" s="19">
-        <v>143</v>
+        <v>194</v>
       </c>
     </row>
     <row r="250" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12933,7 +12933,7 @@
         <v>61</v>
       </c>
       <c r="I250" s="19">
-        <v>176</v>
+        <v>329</v>
       </c>
     </row>
     <row r="251" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12962,7 +12962,7 @@
         <v>52</v>
       </c>
       <c r="I251" s="19">
-        <v>189</v>
+        <v>271</v>
       </c>
     </row>
     <row r="252" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12991,7 +12991,7 @@
         <v>52</v>
       </c>
       <c r="I252" s="19">
-        <v>268</v>
+        <v>443</v>
       </c>
     </row>
     <row r="253" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13020,7 +13020,7 @@
         <v>61</v>
       </c>
       <c r="I253" s="19">
-        <v>509</v>
+        <v>296</v>
       </c>
     </row>
     <row r="254" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13049,7 +13049,7 @@
         <v>52</v>
       </c>
       <c r="I254" s="19">
-        <v>246</v>
+        <v>192</v>
       </c>
     </row>
     <row r="255" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13078,7 +13078,7 @@
         <v>52</v>
       </c>
       <c r="I255" s="19">
-        <v>131</v>
+        <v>451</v>
       </c>
     </row>
     <row r="256" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13107,7 +13107,7 @@
         <v>61</v>
       </c>
       <c r="I256" s="19">
-        <v>231</v>
+        <v>479</v>
       </c>
     </row>
     <row r="257" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13136,7 +13136,7 @@
         <v>52</v>
       </c>
       <c r="I257" s="19">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="258" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13165,7 +13165,7 @@
         <v>52</v>
       </c>
       <c r="I258" s="19">
-        <v>422</v>
+        <v>360</v>
       </c>
     </row>
     <row r="259" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13194,7 +13194,7 @@
         <v>61</v>
       </c>
       <c r="I259" s="19">
-        <v>317</v>
+        <v>482</v>
       </c>
     </row>
     <row r="260" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13223,7 +13223,7 @@
         <v>52</v>
       </c>
       <c r="I260" s="19">
-        <v>509</v>
+        <v>462</v>
       </c>
     </row>
     <row r="261" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13252,7 +13252,7 @@
         <v>52</v>
       </c>
       <c r="I261" s="19">
-        <v>284</v>
+        <v>377</v>
       </c>
     </row>
     <row r="262" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13281,7 +13281,7 @@
         <v>61</v>
       </c>
       <c r="I262" s="19">
-        <v>187</v>
+        <v>351</v>
       </c>
     </row>
     <row r="263" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13310,7 +13310,7 @@
         <v>52</v>
       </c>
       <c r="I263" s="19">
-        <v>155</v>
+        <v>271</v>
       </c>
     </row>
     <row r="264" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13339,7 +13339,7 @@
         <v>52</v>
       </c>
       <c r="I264" s="19">
-        <v>282</v>
+        <v>502</v>
       </c>
     </row>
     <row r="265" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13368,7 +13368,7 @@
         <v>61</v>
       </c>
       <c r="I265" s="19">
-        <v>248</v>
+        <v>507</v>
       </c>
     </row>
     <row r="266" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13397,7 +13397,7 @@
         <v>52</v>
       </c>
       <c r="I266" s="19">
-        <v>288</v>
+        <v>253</v>
       </c>
     </row>
     <row r="267" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13426,7 +13426,7 @@
         <v>52</v>
       </c>
       <c r="I267" s="19">
-        <v>202</v>
+        <v>243</v>
       </c>
     </row>
     <row r="268" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13455,7 +13455,7 @@
         <v>61</v>
       </c>
       <c r="I268" s="19">
-        <v>169</v>
+        <v>263</v>
       </c>
     </row>
     <row r="269" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13484,7 +13484,7 @@
         <v>52</v>
       </c>
       <c r="I269" s="19">
-        <v>304</v>
+        <v>134</v>
       </c>
     </row>
     <row r="270" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13513,7 +13513,7 @@
         <v>52</v>
       </c>
       <c r="I270" s="19">
-        <v>415</v>
+        <v>248</v>
       </c>
     </row>
     <row r="271" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13542,7 +13542,7 @@
         <v>61</v>
       </c>
       <c r="I271" s="19">
-        <v>512</v>
+        <v>124</v>
       </c>
     </row>
     <row r="272" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13571,7 +13571,7 @@
         <v>52</v>
       </c>
       <c r="I272" s="19">
-        <v>333</v>
+        <v>200</v>
       </c>
     </row>
     <row r="273" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13600,7 +13600,7 @@
         <v>52</v>
       </c>
       <c r="I273" s="19">
-        <v>509</v>
+        <v>401</v>
       </c>
     </row>
     <row r="274" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13629,7 +13629,7 @@
         <v>61</v>
       </c>
       <c r="I274" s="19">
-        <v>374</v>
+        <v>473</v>
       </c>
     </row>
     <row r="275" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13658,7 +13658,7 @@
         <v>52</v>
       </c>
       <c r="I275" s="19">
-        <v>517</v>
+        <v>457</v>
       </c>
     </row>
     <row r="276" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13687,7 +13687,7 @@
         <v>273</v>
       </c>
       <c r="I276" s="19">
-        <v>426</v>
+        <v>242</v>
       </c>
     </row>
     <row r="277" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13716,7 +13716,7 @@
         <v>61</v>
       </c>
       <c r="I277" s="19">
-        <v>235</v>
+        <v>246</v>
       </c>
     </row>
     <row r="278" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13745,7 +13745,7 @@
         <v>52</v>
       </c>
       <c r="I278" s="19">
-        <v>240</v>
+        <v>146</v>
       </c>
     </row>
     <row r="279" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13774,7 +13774,7 @@
         <v>52</v>
       </c>
       <c r="I279" s="19">
-        <v>148</v>
+        <v>467</v>
       </c>
     </row>
     <row r="280" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13803,7 +13803,7 @@
         <v>61</v>
       </c>
       <c r="I280" s="19">
-        <v>134</v>
+        <v>221</v>
       </c>
     </row>
     <row r="281" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13832,7 +13832,7 @@
         <v>52</v>
       </c>
       <c r="I281" s="19">
-        <v>330</v>
+        <v>260</v>
       </c>
     </row>
     <row r="282" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13861,7 +13861,7 @@
         <v>52</v>
       </c>
       <c r="I282" s="19">
-        <v>356</v>
+        <v>177</v>
       </c>
     </row>
     <row r="283" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13890,7 +13890,7 @@
         <v>61</v>
       </c>
       <c r="I283" s="19">
-        <v>283</v>
+        <v>126</v>
       </c>
     </row>
     <row r="284" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13919,7 +13919,7 @@
         <v>52</v>
       </c>
       <c r="I284" s="19">
-        <v>333</v>
+        <v>368</v>
       </c>
     </row>
     <row r="285" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13948,7 +13948,7 @@
         <v>52</v>
       </c>
       <c r="I285" s="19">
-        <v>194</v>
+        <v>506</v>
       </c>
     </row>
     <row r="286" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13977,7 +13977,7 @@
         <v>61</v>
       </c>
       <c r="I286" s="19">
-        <v>156</v>
+        <v>283</v>
       </c>
     </row>
     <row r="287" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14006,7 +14006,7 @@
         <v>52</v>
       </c>
       <c r="I287" s="19">
-        <v>138</v>
+        <v>154</v>
       </c>
     </row>
     <row r="288" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14035,7 +14035,7 @@
         <v>52</v>
       </c>
       <c r="I288" s="19">
-        <v>126</v>
+        <v>439</v>
       </c>
     </row>
     <row r="289" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14064,7 +14064,7 @@
         <v>61</v>
       </c>
       <c r="I289" s="19">
-        <v>280</v>
+        <v>132</v>
       </c>
     </row>
     <row r="290" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14093,7 +14093,7 @@
         <v>52</v>
       </c>
       <c r="I290" s="19">
-        <v>150</v>
+        <v>484</v>
       </c>
     </row>
     <row r="291" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14122,7 +14122,7 @@
         <v>52</v>
       </c>
       <c r="I291" s="19">
-        <v>346</v>
+        <v>484</v>
       </c>
     </row>
     <row r="292" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14151,7 +14151,7 @@
         <v>61</v>
       </c>
       <c r="I292" s="19">
-        <v>145</v>
+        <v>338</v>
       </c>
     </row>
     <row r="293" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14180,7 +14180,7 @@
         <v>52</v>
       </c>
       <c r="I293" s="19">
-        <v>396</v>
+        <v>121</v>
       </c>
     </row>
     <row r="294" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14209,7 +14209,7 @@
         <v>52</v>
       </c>
       <c r="I294" s="19">
-        <v>474</v>
+        <v>159</v>
       </c>
     </row>
     <row r="295" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14238,7 +14238,7 @@
         <v>61</v>
       </c>
       <c r="I295" s="19">
-        <v>128</v>
+        <v>359</v>
       </c>
     </row>
     <row r="296" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14267,7 +14267,7 @@
         <v>52</v>
       </c>
       <c r="I296" s="19">
-        <v>239</v>
+        <v>130</v>
       </c>
     </row>
     <row r="297" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14296,7 +14296,7 @@
         <v>52</v>
       </c>
       <c r="I297" s="19">
-        <v>324</v>
+        <v>350</v>
       </c>
     </row>
     <row r="298" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14325,7 +14325,7 @@
         <v>61</v>
       </c>
       <c r="I298" s="19">
-        <v>345</v>
+        <v>395</v>
       </c>
     </row>
     <row r="299" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14354,7 +14354,7 @@
         <v>52</v>
       </c>
       <c r="I299" s="19">
-        <v>417</v>
+        <v>222</v>
       </c>
     </row>
     <row r="300" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14383,7 +14383,7 @@
         <v>52</v>
       </c>
       <c r="I300" s="19">
-        <v>276</v>
+        <v>294</v>
       </c>
     </row>
     <row r="301" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14412,7 +14412,7 @@
         <v>61</v>
       </c>
       <c r="I301" s="19">
-        <v>278</v>
+        <v>315</v>
       </c>
     </row>
     <row r="302" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14441,7 +14441,7 @@
         <v>52</v>
       </c>
       <c r="I302" s="19">
-        <v>312</v>
+        <v>158</v>
       </c>
     </row>
     <row r="303" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14470,7 +14470,7 @@
         <v>52</v>
       </c>
       <c r="I303" s="19">
-        <v>384</v>
+        <v>445</v>
       </c>
     </row>
     <row r="304" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14499,7 +14499,7 @@
         <v>61</v>
       </c>
       <c r="I304" s="19">
-        <v>517</v>
+        <v>321</v>
       </c>
     </row>
     <row r="305" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14528,7 +14528,7 @@
         <v>52</v>
       </c>
       <c r="I305" s="19">
-        <v>159</v>
+        <v>241</v>
       </c>
     </row>
     <row r="306" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14557,7 +14557,7 @@
         <v>52</v>
       </c>
       <c r="I306" s="19">
-        <v>197</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>

--- a/selenium-tests/Test_Summary_and_Details_Report.xlsx
+++ b/selenium-tests/Test_Summary_and_Details_Report.xlsx
@@ -5741,7 +5741,7 @@
         <v>52</v>
       </c>
       <c r="I2" s="19">
-        <v>209</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5770,7 +5770,7 @@
         <v>52</v>
       </c>
       <c r="I3" s="19">
-        <v>124</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5799,7 +5799,7 @@
         <v>61</v>
       </c>
       <c r="I4" s="19">
-        <v>486</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5828,7 +5828,7 @@
         <v>52</v>
       </c>
       <c r="I5" s="19">
-        <v>210</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5857,7 +5857,7 @@
         <v>52</v>
       </c>
       <c r="I6" s="19">
-        <v>517</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5886,7 +5886,7 @@
         <v>61</v>
       </c>
       <c r="I7" s="19">
-        <v>166</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5915,7 +5915,7 @@
         <v>52</v>
       </c>
       <c r="I8" s="19">
-        <v>230</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5944,7 +5944,7 @@
         <v>52</v>
       </c>
       <c r="I9" s="19">
-        <v>215</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5973,7 +5973,7 @@
         <v>61</v>
       </c>
       <c r="I10" s="19">
-        <v>514</v>
+        <v>472</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6002,7 +6002,7 @@
         <v>52</v>
       </c>
       <c r="I11" s="19">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6031,7 +6031,7 @@
         <v>52</v>
       </c>
       <c r="I12" s="19">
-        <v>385</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6060,7 +6060,7 @@
         <v>61</v>
       </c>
       <c r="I13" s="19">
-        <v>214</v>
+        <v>502</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6089,7 +6089,7 @@
         <v>52</v>
       </c>
       <c r="I14" s="19">
-        <v>489</v>
+        <v>338</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6118,7 +6118,7 @@
         <v>52</v>
       </c>
       <c r="I15" s="19">
-        <v>375</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6147,7 +6147,7 @@
         <v>61</v>
       </c>
       <c r="I16" s="19">
-        <v>223</v>
+        <v>499</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6176,7 +6176,7 @@
         <v>52</v>
       </c>
       <c r="I17" s="19">
-        <v>180</v>
+        <v>464</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6205,7 +6205,7 @@
         <v>52</v>
       </c>
       <c r="I18" s="19">
-        <v>216</v>
+        <v>361</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6234,7 +6234,7 @@
         <v>61</v>
       </c>
       <c r="I19" s="19">
-        <v>478</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6263,7 +6263,7 @@
         <v>52</v>
       </c>
       <c r="I20" s="19">
-        <v>282</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6292,7 +6292,7 @@
         <v>52</v>
       </c>
       <c r="I21" s="19">
-        <v>453</v>
+        <v>509</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6321,7 +6321,7 @@
         <v>61</v>
       </c>
       <c r="I22" s="19">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6350,7 +6350,7 @@
         <v>52</v>
       </c>
       <c r="I23" s="19">
-        <v>227</v>
+        <v>395</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6379,7 +6379,7 @@
         <v>52</v>
       </c>
       <c r="I24" s="19">
-        <v>449</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6408,7 +6408,7 @@
         <v>61</v>
       </c>
       <c r="I25" s="19">
-        <v>357</v>
+        <v>421</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6437,7 +6437,7 @@
         <v>52</v>
       </c>
       <c r="I26" s="19">
-        <v>186</v>
+        <v>317</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6466,7 +6466,7 @@
         <v>52</v>
       </c>
       <c r="I27" s="19">
-        <v>358</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6495,7 +6495,7 @@
         <v>61</v>
       </c>
       <c r="I28" s="19">
-        <v>260</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6524,7 +6524,7 @@
         <v>52</v>
       </c>
       <c r="I29" s="19">
-        <v>465</v>
+        <v>485</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6553,7 +6553,7 @@
         <v>52</v>
       </c>
       <c r="I30" s="19">
-        <v>214</v>
+        <v>451</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6582,7 +6582,7 @@
         <v>61</v>
       </c>
       <c r="I31" s="19">
-        <v>351</v>
+        <v>337</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6611,7 +6611,7 @@
         <v>52</v>
       </c>
       <c r="I32" s="19">
-        <v>299</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6640,7 +6640,7 @@
         <v>52</v>
       </c>
       <c r="I33" s="19">
-        <v>152</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6669,7 +6669,7 @@
         <v>61</v>
       </c>
       <c r="I34" s="19">
-        <v>137</v>
+        <v>322</v>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6698,7 +6698,7 @@
         <v>52</v>
       </c>
       <c r="I35" s="19">
-        <v>136</v>
+        <v>421</v>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6727,7 +6727,7 @@
         <v>52</v>
       </c>
       <c r="I36" s="19">
-        <v>393</v>
+        <v>497</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6756,7 +6756,7 @@
         <v>61</v>
       </c>
       <c r="I37" s="19">
-        <v>172</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6785,7 +6785,7 @@
         <v>52</v>
       </c>
       <c r="I38" s="19">
-        <v>150</v>
+        <v>356</v>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6814,7 +6814,7 @@
         <v>52</v>
       </c>
       <c r="I39" s="19">
-        <v>271</v>
+        <v>148</v>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6843,7 +6843,7 @@
         <v>61</v>
       </c>
       <c r="I40" s="19">
-        <v>352</v>
+        <v>468</v>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6872,7 +6872,7 @@
         <v>52</v>
       </c>
       <c r="I41" s="19">
-        <v>485</v>
+        <v>324</v>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6901,7 +6901,7 @@
         <v>52</v>
       </c>
       <c r="I42" s="19">
-        <v>181</v>
+        <v>462</v>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6930,7 +6930,7 @@
         <v>61</v>
       </c>
       <c r="I43" s="19">
-        <v>393</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6959,7 +6959,7 @@
         <v>52</v>
       </c>
       <c r="I44" s="19">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6988,7 +6988,7 @@
         <v>52</v>
       </c>
       <c r="I45" s="19">
-        <v>289</v>
+        <v>331</v>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7017,7 +7017,7 @@
         <v>61</v>
       </c>
       <c r="I46" s="19">
-        <v>489</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7046,7 +7046,7 @@
         <v>52</v>
       </c>
       <c r="I47" s="19">
-        <v>496</v>
+        <v>302</v>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7075,7 +7075,7 @@
         <v>52</v>
       </c>
       <c r="I48" s="19">
-        <v>363</v>
+        <v>392</v>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7104,7 +7104,7 @@
         <v>61</v>
       </c>
       <c r="I49" s="19">
-        <v>426</v>
+        <v>263</v>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7133,7 +7133,7 @@
         <v>52</v>
       </c>
       <c r="I50" s="19">
-        <v>497</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7162,7 +7162,7 @@
         <v>52</v>
       </c>
       <c r="I51" s="19">
-        <v>394</v>
+        <v>352</v>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7191,7 +7191,7 @@
         <v>61</v>
       </c>
       <c r="I52" s="19">
-        <v>195</v>
+        <v>380</v>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7220,7 +7220,7 @@
         <v>52</v>
       </c>
       <c r="I53" s="19">
-        <v>327</v>
+        <v>361</v>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7249,7 +7249,7 @@
         <v>52</v>
       </c>
       <c r="I54" s="19">
-        <v>479</v>
+        <v>198</v>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7278,7 +7278,7 @@
         <v>61</v>
       </c>
       <c r="I55" s="19">
-        <v>384</v>
+        <v>145</v>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7307,7 +7307,7 @@
         <v>273</v>
       </c>
       <c r="I56" s="19">
-        <v>440</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7336,7 +7336,7 @@
         <v>52</v>
       </c>
       <c r="I57" s="19">
-        <v>217</v>
+        <v>253</v>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7365,7 +7365,7 @@
         <v>61</v>
       </c>
       <c r="I58" s="19">
-        <v>372</v>
+        <v>334</v>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7394,7 +7394,7 @@
         <v>52</v>
       </c>
       <c r="I59" s="19">
-        <v>249</v>
+        <v>373</v>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7423,7 +7423,7 @@
         <v>52</v>
       </c>
       <c r="I60" s="19">
-        <v>430</v>
+        <v>460</v>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7452,7 +7452,7 @@
         <v>61</v>
       </c>
       <c r="I61" s="19">
-        <v>500</v>
+        <v>201</v>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7481,7 +7481,7 @@
         <v>52</v>
       </c>
       <c r="I62" s="19">
-        <v>311</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7510,7 +7510,7 @@
         <v>52</v>
       </c>
       <c r="I63" s="19">
-        <v>428</v>
+        <v>471</v>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7539,7 +7539,7 @@
         <v>61</v>
       </c>
       <c r="I64" s="19">
-        <v>351</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7568,7 +7568,7 @@
         <v>52</v>
       </c>
       <c r="I65" s="19">
-        <v>129</v>
+        <v>269</v>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7597,7 +7597,7 @@
         <v>52</v>
       </c>
       <c r="I66" s="19">
-        <v>162</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7626,7 +7626,7 @@
         <v>61</v>
       </c>
       <c r="I67" s="19">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7655,7 +7655,7 @@
         <v>52</v>
       </c>
       <c r="I68" s="19">
-        <v>374</v>
+        <v>279</v>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7684,7 +7684,7 @@
         <v>52</v>
       </c>
       <c r="I69" s="19">
-        <v>178</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7713,7 +7713,7 @@
         <v>61</v>
       </c>
       <c r="I70" s="19">
-        <v>476</v>
+        <v>419</v>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7742,7 +7742,7 @@
         <v>52</v>
       </c>
       <c r="I71" s="19">
-        <v>411</v>
+        <v>180</v>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7771,7 +7771,7 @@
         <v>52</v>
       </c>
       <c r="I72" s="19">
-        <v>171</v>
+        <v>343</v>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7800,7 +7800,7 @@
         <v>61</v>
       </c>
       <c r="I73" s="19">
-        <v>456</v>
+        <v>139</v>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7829,7 +7829,7 @@
         <v>52</v>
       </c>
       <c r="I74" s="19">
-        <v>306</v>
+        <v>240</v>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7858,7 +7858,7 @@
         <v>52</v>
       </c>
       <c r="I75" s="19">
-        <v>465</v>
+        <v>375</v>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7887,7 +7887,7 @@
         <v>61</v>
       </c>
       <c r="I76" s="19">
-        <v>367</v>
+        <v>310</v>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7916,7 +7916,7 @@
         <v>52</v>
       </c>
       <c r="I77" s="19">
-        <v>482</v>
+        <v>324</v>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7945,7 +7945,7 @@
         <v>52</v>
       </c>
       <c r="I78" s="19">
-        <v>458</v>
+        <v>468</v>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7974,7 +7974,7 @@
         <v>61</v>
       </c>
       <c r="I79" s="19">
-        <v>406</v>
+        <v>299</v>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8003,7 +8003,7 @@
         <v>52</v>
       </c>
       <c r="I80" s="19">
-        <v>426</v>
+        <v>224</v>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8032,7 +8032,7 @@
         <v>52</v>
       </c>
       <c r="I81" s="19">
-        <v>386</v>
+        <v>370</v>
       </c>
     </row>
     <row r="82" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8061,7 +8061,7 @@
         <v>61</v>
       </c>
       <c r="I82" s="19">
-        <v>191</v>
+        <v>137</v>
       </c>
     </row>
     <row r="83" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8090,7 +8090,7 @@
         <v>52</v>
       </c>
       <c r="I83" s="19">
-        <v>507</v>
+        <v>480</v>
       </c>
     </row>
     <row r="84" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8119,7 +8119,7 @@
         <v>52</v>
       </c>
       <c r="I84" s="19">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8148,7 +8148,7 @@
         <v>61</v>
       </c>
       <c r="I85" s="19">
-        <v>249</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8177,7 +8177,7 @@
         <v>52</v>
       </c>
       <c r="I86" s="19">
-        <v>272</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8206,7 +8206,7 @@
         <v>52</v>
       </c>
       <c r="I87" s="19">
-        <v>419</v>
+        <v>413</v>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8235,7 +8235,7 @@
         <v>61</v>
       </c>
       <c r="I88" s="19">
-        <v>281</v>
+        <v>509</v>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8264,7 +8264,7 @@
         <v>52</v>
       </c>
       <c r="I89" s="19">
-        <v>307</v>
+        <v>517</v>
       </c>
     </row>
     <row r="90" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8293,7 +8293,7 @@
         <v>52</v>
       </c>
       <c r="I90" s="19">
-        <v>305</v>
+        <v>229</v>
       </c>
     </row>
     <row r="91" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8322,7 +8322,7 @@
         <v>61</v>
       </c>
       <c r="I91" s="19">
-        <v>345</v>
+        <v>503</v>
       </c>
     </row>
     <row r="92" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8351,7 +8351,7 @@
         <v>52</v>
       </c>
       <c r="I92" s="19">
-        <v>410</v>
+        <v>121</v>
       </c>
     </row>
     <row r="93" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8380,7 +8380,7 @@
         <v>52</v>
       </c>
       <c r="I93" s="19">
-        <v>193</v>
+        <v>124</v>
       </c>
     </row>
     <row r="94" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8409,7 +8409,7 @@
         <v>61</v>
       </c>
       <c r="I94" s="19">
-        <v>329</v>
+        <v>492</v>
       </c>
     </row>
     <row r="95" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8438,7 +8438,7 @@
         <v>52</v>
       </c>
       <c r="I95" s="19">
-        <v>348</v>
+        <v>170</v>
       </c>
     </row>
     <row r="96" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8467,7 +8467,7 @@
         <v>52</v>
       </c>
       <c r="I96" s="19">
-        <v>268</v>
+        <v>307</v>
       </c>
     </row>
     <row r="97" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8496,7 +8496,7 @@
         <v>61</v>
       </c>
       <c r="I97" s="19">
-        <v>221</v>
+        <v>259</v>
       </c>
     </row>
     <row r="98" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8525,7 +8525,7 @@
         <v>52</v>
       </c>
       <c r="I98" s="19">
-        <v>447</v>
+        <v>133</v>
       </c>
     </row>
     <row r="99" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8554,7 +8554,7 @@
         <v>52</v>
       </c>
       <c r="I99" s="19">
-        <v>140</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8583,7 +8583,7 @@
         <v>61</v>
       </c>
       <c r="I100" s="19">
-        <v>420</v>
+        <v>354</v>
       </c>
     </row>
     <row r="101" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8612,7 +8612,7 @@
         <v>52</v>
       </c>
       <c r="I101" s="19">
-        <v>265</v>
+        <v>369</v>
       </c>
     </row>
     <row r="102" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8641,7 +8641,7 @@
         <v>52</v>
       </c>
       <c r="I102" s="19">
-        <v>314</v>
+        <v>427</v>
       </c>
     </row>
     <row r="103" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8670,7 +8670,7 @@
         <v>61</v>
       </c>
       <c r="I103" s="19">
-        <v>402</v>
+        <v>274</v>
       </c>
     </row>
     <row r="104" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8699,7 +8699,7 @@
         <v>52</v>
       </c>
       <c r="I104" s="19">
-        <v>396</v>
+        <v>279</v>
       </c>
     </row>
     <row r="105" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8728,7 +8728,7 @@
         <v>52</v>
       </c>
       <c r="I105" s="19">
-        <v>458</v>
+        <v>351</v>
       </c>
     </row>
     <row r="106" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8757,7 +8757,7 @@
         <v>61</v>
       </c>
       <c r="I106" s="19">
-        <v>249</v>
+        <v>335</v>
       </c>
     </row>
     <row r="107" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8786,7 +8786,7 @@
         <v>52</v>
       </c>
       <c r="I107" s="19">
-        <v>328</v>
+        <v>281</v>
       </c>
     </row>
     <row r="108" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8815,7 +8815,7 @@
         <v>52</v>
       </c>
       <c r="I108" s="19">
-        <v>194</v>
+        <v>134</v>
       </c>
     </row>
     <row r="109" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8844,7 +8844,7 @@
         <v>61</v>
       </c>
       <c r="I109" s="19">
-        <v>195</v>
+        <v>241</v>
       </c>
     </row>
     <row r="110" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8873,7 +8873,7 @@
         <v>52</v>
       </c>
       <c r="I110" s="19">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="111" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8902,7 +8902,7 @@
         <v>273</v>
       </c>
       <c r="I111" s="19">
-        <v>220</v>
+        <v>127</v>
       </c>
     </row>
     <row r="112" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8931,7 +8931,7 @@
         <v>61</v>
       </c>
       <c r="I112" s="19">
-        <v>312</v>
+        <v>471</v>
       </c>
     </row>
     <row r="113" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8960,7 +8960,7 @@
         <v>52</v>
       </c>
       <c r="I113" s="19">
-        <v>328</v>
+        <v>151</v>
       </c>
     </row>
     <row r="114" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8989,7 +8989,7 @@
         <v>52</v>
       </c>
       <c r="I114" s="19">
-        <v>365</v>
+        <v>226</v>
       </c>
     </row>
     <row r="115" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9018,7 +9018,7 @@
         <v>61</v>
       </c>
       <c r="I115" s="19">
-        <v>463</v>
+        <v>228</v>
       </c>
     </row>
     <row r="116" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9047,7 +9047,7 @@
         <v>52</v>
       </c>
       <c r="I116" s="19">
-        <v>130</v>
+        <v>402</v>
       </c>
     </row>
     <row r="117" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9076,7 +9076,7 @@
         <v>52</v>
       </c>
       <c r="I117" s="19">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="118" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9105,7 +9105,7 @@
         <v>61</v>
       </c>
       <c r="I118" s="19">
-        <v>348</v>
+        <v>446</v>
       </c>
     </row>
     <row r="119" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9134,7 +9134,7 @@
         <v>52</v>
       </c>
       <c r="I119" s="19">
-        <v>270</v>
+        <v>240</v>
       </c>
     </row>
     <row r="120" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9163,7 +9163,7 @@
         <v>52</v>
       </c>
       <c r="I120" s="19">
-        <v>477</v>
+        <v>128</v>
       </c>
     </row>
     <row r="121" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9192,7 +9192,7 @@
         <v>61</v>
       </c>
       <c r="I121" s="19">
-        <v>332</v>
+        <v>300</v>
       </c>
     </row>
     <row r="122" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9221,7 +9221,7 @@
         <v>52</v>
       </c>
       <c r="I122" s="19">
-        <v>434</v>
+        <v>512</v>
       </c>
     </row>
     <row r="123" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9250,7 +9250,7 @@
         <v>52</v>
       </c>
       <c r="I123" s="19">
-        <v>343</v>
+        <v>303</v>
       </c>
     </row>
     <row r="124" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9279,7 +9279,7 @@
         <v>61</v>
       </c>
       <c r="I124" s="19">
-        <v>433</v>
+        <v>364</v>
       </c>
     </row>
     <row r="125" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9308,7 +9308,7 @@
         <v>52</v>
       </c>
       <c r="I125" s="19">
-        <v>163</v>
+        <v>377</v>
       </c>
     </row>
     <row r="126" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9337,7 +9337,7 @@
         <v>52</v>
       </c>
       <c r="I126" s="19">
-        <v>397</v>
+        <v>248</v>
       </c>
     </row>
     <row r="127" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9366,7 +9366,7 @@
         <v>61</v>
       </c>
       <c r="I127" s="19">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="128" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9395,7 +9395,7 @@
         <v>52</v>
       </c>
       <c r="I128" s="19">
-        <v>202</v>
+        <v>356</v>
       </c>
     </row>
     <row r="129" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9424,7 +9424,7 @@
         <v>52</v>
       </c>
       <c r="I129" s="19">
-        <v>375</v>
+        <v>416</v>
       </c>
     </row>
     <row r="130" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9453,7 +9453,7 @@
         <v>61</v>
       </c>
       <c r="I130" s="19">
-        <v>339</v>
+        <v>129</v>
       </c>
     </row>
     <row r="131" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9482,7 +9482,7 @@
         <v>52</v>
       </c>
       <c r="I131" s="19">
-        <v>289</v>
+        <v>411</v>
       </c>
     </row>
     <row r="132" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9511,7 +9511,7 @@
         <v>52</v>
       </c>
       <c r="I132" s="19">
-        <v>501</v>
+        <v>244</v>
       </c>
     </row>
     <row r="133" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9540,7 +9540,7 @@
         <v>61</v>
       </c>
       <c r="I133" s="19">
-        <v>407</v>
+        <v>417</v>
       </c>
     </row>
     <row r="134" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9569,7 +9569,7 @@
         <v>52</v>
       </c>
       <c r="I134" s="19">
-        <v>432</v>
+        <v>284</v>
       </c>
     </row>
     <row r="135" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9598,7 +9598,7 @@
         <v>52</v>
       </c>
       <c r="I135" s="19">
-        <v>144</v>
+        <v>229</v>
       </c>
     </row>
     <row r="136" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9627,7 +9627,7 @@
         <v>61</v>
       </c>
       <c r="I136" s="19">
-        <v>199</v>
+        <v>177</v>
       </c>
     </row>
     <row r="137" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9656,7 +9656,7 @@
         <v>52</v>
       </c>
       <c r="I137" s="19">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="138" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9685,7 +9685,7 @@
         <v>52</v>
       </c>
       <c r="I138" s="19">
-        <v>236</v>
+        <v>351</v>
       </c>
     </row>
     <row r="139" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9714,7 +9714,7 @@
         <v>61</v>
       </c>
       <c r="I139" s="19">
-        <v>420</v>
+        <v>132</v>
       </c>
     </row>
     <row r="140" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9743,7 +9743,7 @@
         <v>52</v>
       </c>
       <c r="I140" s="19">
-        <v>228</v>
+        <v>183</v>
       </c>
     </row>
     <row r="141" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9772,7 +9772,7 @@
         <v>52</v>
       </c>
       <c r="I141" s="19">
-        <v>255</v>
+        <v>380</v>
       </c>
     </row>
     <row r="142" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9801,7 +9801,7 @@
         <v>61</v>
       </c>
       <c r="I142" s="19">
-        <v>328</v>
+        <v>170</v>
       </c>
     </row>
     <row r="143" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9830,7 +9830,7 @@
         <v>52</v>
       </c>
       <c r="I143" s="19">
-        <v>253</v>
+        <v>415</v>
       </c>
     </row>
     <row r="144" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9859,7 +9859,7 @@
         <v>52</v>
       </c>
       <c r="I144" s="19">
-        <v>378</v>
+        <v>432</v>
       </c>
     </row>
     <row r="145" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9888,7 +9888,7 @@
         <v>61</v>
       </c>
       <c r="I145" s="19">
-        <v>158</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9917,7 +9917,7 @@
         <v>52</v>
       </c>
       <c r="I146" s="19">
-        <v>183</v>
+        <v>405</v>
       </c>
     </row>
     <row r="147" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9946,7 +9946,7 @@
         <v>52</v>
       </c>
       <c r="I147" s="19">
-        <v>341</v>
+        <v>417</v>
       </c>
     </row>
     <row r="148" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9975,7 +9975,7 @@
         <v>61</v>
       </c>
       <c r="I148" s="19">
-        <v>155</v>
+        <v>512</v>
       </c>
     </row>
     <row r="149" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10004,7 +10004,7 @@
         <v>52</v>
       </c>
       <c r="I149" s="19">
-        <v>303</v>
+        <v>145</v>
       </c>
     </row>
     <row r="150" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10033,7 +10033,7 @@
         <v>52</v>
       </c>
       <c r="I150" s="19">
-        <v>183</v>
+        <v>357</v>
       </c>
     </row>
     <row r="151" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10062,7 +10062,7 @@
         <v>61</v>
       </c>
       <c r="I151" s="19">
-        <v>417</v>
+        <v>140</v>
       </c>
     </row>
     <row r="152" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10091,7 +10091,7 @@
         <v>52</v>
       </c>
       <c r="I152" s="19">
-        <v>168</v>
+        <v>397</v>
       </c>
     </row>
     <row r="153" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10120,7 +10120,7 @@
         <v>52</v>
       </c>
       <c r="I153" s="19">
-        <v>496</v>
+        <v>319</v>
       </c>
     </row>
     <row r="154" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10149,7 +10149,7 @@
         <v>61</v>
       </c>
       <c r="I154" s="19">
-        <v>285</v>
+        <v>194</v>
       </c>
     </row>
     <row r="155" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10178,7 +10178,7 @@
         <v>52</v>
       </c>
       <c r="I155" s="19">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="156" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10207,7 +10207,7 @@
         <v>52</v>
       </c>
       <c r="I156" s="19">
-        <v>236</v>
+        <v>152</v>
       </c>
     </row>
     <row r="157" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10236,7 +10236,7 @@
         <v>61</v>
       </c>
       <c r="I157" s="19">
-        <v>389</v>
+        <v>369</v>
       </c>
     </row>
     <row r="158" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10265,7 +10265,7 @@
         <v>52</v>
       </c>
       <c r="I158" s="19">
-        <v>350</v>
+        <v>204</v>
       </c>
     </row>
     <row r="159" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10294,7 +10294,7 @@
         <v>52</v>
       </c>
       <c r="I159" s="19">
-        <v>377</v>
+        <v>178</v>
       </c>
     </row>
     <row r="160" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10323,7 +10323,7 @@
         <v>61</v>
       </c>
       <c r="I160" s="19">
-        <v>144</v>
+        <v>125</v>
       </c>
     </row>
     <row r="161" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10352,7 +10352,7 @@
         <v>52</v>
       </c>
       <c r="I161" s="19">
-        <v>397</v>
+        <v>295</v>
       </c>
     </row>
     <row r="162" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10381,7 +10381,7 @@
         <v>52</v>
       </c>
       <c r="I162" s="19">
-        <v>501</v>
+        <v>365</v>
       </c>
     </row>
     <row r="163" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10410,7 +10410,7 @@
         <v>61</v>
       </c>
       <c r="I163" s="19">
-        <v>311</v>
+        <v>200</v>
       </c>
     </row>
     <row r="164" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10439,7 +10439,7 @@
         <v>52</v>
       </c>
       <c r="I164" s="19">
-        <v>321</v>
+        <v>343</v>
       </c>
     </row>
     <row r="165" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10468,7 +10468,7 @@
         <v>52</v>
       </c>
       <c r="I165" s="19">
-        <v>340</v>
+        <v>491</v>
       </c>
     </row>
     <row r="166" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10497,7 +10497,7 @@
         <v>273</v>
       </c>
       <c r="I166" s="19">
-        <v>364</v>
+        <v>164</v>
       </c>
     </row>
     <row r="167" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10526,7 +10526,7 @@
         <v>52</v>
       </c>
       <c r="I167" s="19">
-        <v>231</v>
+        <v>206</v>
       </c>
     </row>
     <row r="168" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10555,7 +10555,7 @@
         <v>52</v>
       </c>
       <c r="I168" s="19">
-        <v>167</v>
+        <v>206</v>
       </c>
     </row>
     <row r="169" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10584,7 +10584,7 @@
         <v>61</v>
       </c>
       <c r="I169" s="19">
-        <v>398</v>
+        <v>272</v>
       </c>
     </row>
     <row r="170" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10613,7 +10613,7 @@
         <v>52</v>
       </c>
       <c r="I170" s="19">
-        <v>349</v>
+        <v>230</v>
       </c>
     </row>
     <row r="171" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10642,7 +10642,7 @@
         <v>52</v>
       </c>
       <c r="I171" s="19">
-        <v>157</v>
+        <v>132</v>
       </c>
     </row>
     <row r="172" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10671,7 +10671,7 @@
         <v>61</v>
       </c>
       <c r="I172" s="19">
-        <v>350</v>
+        <v>235</v>
       </c>
     </row>
     <row r="173" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10700,7 +10700,7 @@
         <v>52</v>
       </c>
       <c r="I173" s="19">
-        <v>167</v>
+        <v>428</v>
       </c>
     </row>
     <row r="174" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10729,7 +10729,7 @@
         <v>52</v>
       </c>
       <c r="I174" s="19">
-        <v>268</v>
+        <v>162</v>
       </c>
     </row>
     <row r="175" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10758,7 +10758,7 @@
         <v>61</v>
       </c>
       <c r="I175" s="19">
-        <v>396</v>
+        <v>487</v>
       </c>
     </row>
     <row r="176" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10787,7 +10787,7 @@
         <v>52</v>
       </c>
       <c r="I176" s="19">
-        <v>390</v>
+        <v>450</v>
       </c>
     </row>
     <row r="177" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10816,7 +10816,7 @@
         <v>52</v>
       </c>
       <c r="I177" s="19">
-        <v>455</v>
+        <v>341</v>
       </c>
     </row>
     <row r="178" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10845,7 +10845,7 @@
         <v>61</v>
       </c>
       <c r="I178" s="19">
-        <v>122</v>
+        <v>311</v>
       </c>
     </row>
     <row r="179" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10874,7 +10874,7 @@
         <v>52</v>
       </c>
       <c r="I179" s="19">
-        <v>223</v>
+        <v>482</v>
       </c>
     </row>
     <row r="180" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10903,7 +10903,7 @@
         <v>52</v>
       </c>
       <c r="I180" s="19">
-        <v>367</v>
+        <v>398</v>
       </c>
     </row>
     <row r="181" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10932,7 +10932,7 @@
         <v>61</v>
       </c>
       <c r="I181" s="19">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="182" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10961,7 +10961,7 @@
         <v>52</v>
       </c>
       <c r="I182" s="19">
-        <v>120</v>
+        <v>401</v>
       </c>
     </row>
     <row r="183" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -10990,7 +10990,7 @@
         <v>52</v>
       </c>
       <c r="I183" s="19">
-        <v>464</v>
+        <v>234</v>
       </c>
     </row>
     <row r="184" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11019,7 +11019,7 @@
         <v>61</v>
       </c>
       <c r="I184" s="19">
-        <v>447</v>
+        <v>266</v>
       </c>
     </row>
     <row r="185" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11048,7 +11048,7 @@
         <v>52</v>
       </c>
       <c r="I185" s="19">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="186" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11077,7 +11077,7 @@
         <v>52</v>
       </c>
       <c r="I186" s="19">
-        <v>434</v>
+        <v>298</v>
       </c>
     </row>
     <row r="187" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11106,7 +11106,7 @@
         <v>61</v>
       </c>
       <c r="I187" s="19">
-        <v>389</v>
+        <v>513</v>
       </c>
     </row>
     <row r="188" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11135,7 +11135,7 @@
         <v>52</v>
       </c>
       <c r="I188" s="19">
-        <v>462</v>
+        <v>355</v>
       </c>
     </row>
     <row r="189" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11164,7 +11164,7 @@
         <v>52</v>
       </c>
       <c r="I189" s="19">
-        <v>346</v>
+        <v>241</v>
       </c>
     </row>
     <row r="190" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11193,7 +11193,7 @@
         <v>61</v>
       </c>
       <c r="I190" s="19">
-        <v>416</v>
+        <v>226</v>
       </c>
     </row>
     <row r="191" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11222,7 +11222,7 @@
         <v>52</v>
       </c>
       <c r="I191" s="19">
-        <v>433</v>
+        <v>359</v>
       </c>
     </row>
     <row r="192" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11251,7 +11251,7 @@
         <v>52</v>
       </c>
       <c r="I192" s="19">
-        <v>124</v>
+        <v>287</v>
       </c>
     </row>
     <row r="193" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11280,7 +11280,7 @@
         <v>61</v>
       </c>
       <c r="I193" s="19">
-        <v>228</v>
+        <v>209</v>
       </c>
     </row>
     <row r="194" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11309,7 +11309,7 @@
         <v>52</v>
       </c>
       <c r="I194" s="19">
-        <v>231</v>
+        <v>319</v>
       </c>
     </row>
     <row r="195" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11338,7 +11338,7 @@
         <v>52</v>
       </c>
       <c r="I195" s="19">
-        <v>132</v>
+        <v>479</v>
       </c>
     </row>
     <row r="196" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11367,7 +11367,7 @@
         <v>61</v>
       </c>
       <c r="I196" s="19">
-        <v>456</v>
+        <v>158</v>
       </c>
     </row>
     <row r="197" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11396,7 +11396,7 @@
         <v>52</v>
       </c>
       <c r="I197" s="19">
-        <v>172</v>
+        <v>506</v>
       </c>
     </row>
     <row r="198" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11425,7 +11425,7 @@
         <v>52</v>
       </c>
       <c r="I198" s="19">
-        <v>265</v>
+        <v>133</v>
       </c>
     </row>
     <row r="199" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11454,7 +11454,7 @@
         <v>61</v>
       </c>
       <c r="I199" s="19">
-        <v>165</v>
+        <v>205</v>
       </c>
     </row>
     <row r="200" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11483,7 +11483,7 @@
         <v>52</v>
       </c>
       <c r="I200" s="19">
-        <v>328</v>
+        <v>502</v>
       </c>
     </row>
     <row r="201" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11512,7 +11512,7 @@
         <v>52</v>
       </c>
       <c r="I201" s="19">
-        <v>223</v>
+        <v>311</v>
       </c>
     </row>
     <row r="202" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11541,7 +11541,7 @@
         <v>61</v>
       </c>
       <c r="I202" s="19">
-        <v>483</v>
+        <v>372</v>
       </c>
     </row>
     <row r="203" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11570,7 +11570,7 @@
         <v>52</v>
       </c>
       <c r="I203" s="19">
-        <v>122</v>
+        <v>459</v>
       </c>
     </row>
     <row r="204" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11599,7 +11599,7 @@
         <v>52</v>
       </c>
       <c r="I204" s="19">
-        <v>407</v>
+        <v>306</v>
       </c>
     </row>
     <row r="205" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11628,7 +11628,7 @@
         <v>61</v>
       </c>
       <c r="I205" s="19">
-        <v>143</v>
+        <v>298</v>
       </c>
     </row>
     <row r="206" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11657,7 +11657,7 @@
         <v>52</v>
       </c>
       <c r="I206" s="19">
-        <v>451</v>
+        <v>222</v>
       </c>
     </row>
     <row r="207" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11686,7 +11686,7 @@
         <v>52</v>
       </c>
       <c r="I207" s="19">
-        <v>462</v>
+        <v>297</v>
       </c>
     </row>
     <row r="208" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11715,7 +11715,7 @@
         <v>61</v>
       </c>
       <c r="I208" s="19">
-        <v>252</v>
+        <v>265</v>
       </c>
     </row>
     <row r="209" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11744,7 +11744,7 @@
         <v>52</v>
       </c>
       <c r="I209" s="19">
-        <v>235</v>
+        <v>207</v>
       </c>
     </row>
     <row r="210" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11773,7 +11773,7 @@
         <v>52</v>
       </c>
       <c r="I210" s="19">
-        <v>294</v>
+        <v>365</v>
       </c>
     </row>
     <row r="211" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11802,7 +11802,7 @@
         <v>61</v>
       </c>
       <c r="I211" s="19">
-        <v>431</v>
+        <v>444</v>
       </c>
     </row>
     <row r="212" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11831,7 +11831,7 @@
         <v>52</v>
       </c>
       <c r="I212" s="19">
-        <v>468</v>
+        <v>250</v>
       </c>
     </row>
     <row r="213" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11860,7 +11860,7 @@
         <v>52</v>
       </c>
       <c r="I213" s="19">
-        <v>432</v>
+        <v>260</v>
       </c>
     </row>
     <row r="214" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11889,7 +11889,7 @@
         <v>61</v>
       </c>
       <c r="I214" s="19">
-        <v>313</v>
+        <v>243</v>
       </c>
     </row>
     <row r="215" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11918,7 +11918,7 @@
         <v>52</v>
       </c>
       <c r="I215" s="19">
-        <v>371</v>
+        <v>498</v>
       </c>
     </row>
     <row r="216" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11947,7 +11947,7 @@
         <v>52</v>
       </c>
       <c r="I216" s="19">
-        <v>334</v>
+        <v>132</v>
       </c>
     </row>
     <row r="217" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -11976,7 +11976,7 @@
         <v>61</v>
       </c>
       <c r="I217" s="19">
-        <v>349</v>
+        <v>253</v>
       </c>
     </row>
     <row r="218" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12005,7 +12005,7 @@
         <v>52</v>
       </c>
       <c r="I218" s="19">
-        <v>190</v>
+        <v>350</v>
       </c>
     </row>
     <row r="219" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12034,7 +12034,7 @@
         <v>52</v>
       </c>
       <c r="I219" s="19">
-        <v>482</v>
+        <v>284</v>
       </c>
     </row>
     <row r="220" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12063,7 +12063,7 @@
         <v>61</v>
       </c>
       <c r="I220" s="19">
-        <v>461</v>
+        <v>314</v>
       </c>
     </row>
     <row r="221" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12092,7 +12092,7 @@
         <v>273</v>
       </c>
       <c r="I221" s="19">
-        <v>317</v>
+        <v>371</v>
       </c>
     </row>
     <row r="222" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12121,7 +12121,7 @@
         <v>52</v>
       </c>
       <c r="I222" s="19">
-        <v>179</v>
+        <v>310</v>
       </c>
     </row>
     <row r="223" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12150,7 +12150,7 @@
         <v>61</v>
       </c>
       <c r="I223" s="19">
-        <v>217</v>
+        <v>511</v>
       </c>
     </row>
     <row r="224" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12179,7 +12179,7 @@
         <v>52</v>
       </c>
       <c r="I224" s="19">
-        <v>245</v>
+        <v>439</v>
       </c>
     </row>
     <row r="225" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12208,7 +12208,7 @@
         <v>52</v>
       </c>
       <c r="I225" s="19">
-        <v>255</v>
+        <v>275</v>
       </c>
     </row>
     <row r="226" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12237,7 +12237,7 @@
         <v>61</v>
       </c>
       <c r="I226" s="19">
-        <v>175</v>
+        <v>246</v>
       </c>
     </row>
     <row r="227" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12266,7 +12266,7 @@
         <v>52</v>
       </c>
       <c r="I227" s="19">
-        <v>155</v>
+        <v>294</v>
       </c>
     </row>
     <row r="228" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12295,7 +12295,7 @@
         <v>52</v>
       </c>
       <c r="I228" s="19">
-        <v>470</v>
+        <v>319</v>
       </c>
     </row>
     <row r="229" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12324,7 +12324,7 @@
         <v>61</v>
       </c>
       <c r="I229" s="19">
-        <v>373</v>
+        <v>432</v>
       </c>
     </row>
     <row r="230" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12353,7 +12353,7 @@
         <v>52</v>
       </c>
       <c r="I230" s="19">
-        <v>123</v>
+        <v>394</v>
       </c>
     </row>
     <row r="231" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12382,7 +12382,7 @@
         <v>52</v>
       </c>
       <c r="I231" s="19">
-        <v>304</v>
+        <v>288</v>
       </c>
     </row>
     <row r="232" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12411,7 +12411,7 @@
         <v>61</v>
       </c>
       <c r="I232" s="19">
-        <v>207</v>
+        <v>436</v>
       </c>
     </row>
     <row r="233" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12440,7 +12440,7 @@
         <v>52</v>
       </c>
       <c r="I233" s="19">
-        <v>499</v>
+        <v>209</v>
       </c>
     </row>
     <row r="234" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12469,7 +12469,7 @@
         <v>52</v>
       </c>
       <c r="I234" s="19">
-        <v>280</v>
+        <v>397</v>
       </c>
     </row>
     <row r="235" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12498,7 +12498,7 @@
         <v>61</v>
       </c>
       <c r="I235" s="19">
-        <v>317</v>
+        <v>197</v>
       </c>
     </row>
     <row r="236" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12527,7 +12527,7 @@
         <v>52</v>
       </c>
       <c r="I236" s="19">
-        <v>129</v>
+        <v>288</v>
       </c>
     </row>
     <row r="237" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12556,7 +12556,7 @@
         <v>52</v>
       </c>
       <c r="I237" s="19">
-        <v>447</v>
+        <v>209</v>
       </c>
     </row>
     <row r="238" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12585,7 +12585,7 @@
         <v>61</v>
       </c>
       <c r="I238" s="19">
-        <v>146</v>
+        <v>518</v>
       </c>
     </row>
     <row r="239" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12614,7 +12614,7 @@
         <v>52</v>
       </c>
       <c r="I239" s="19">
-        <v>131</v>
+        <v>324</v>
       </c>
     </row>
     <row r="240" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12643,7 +12643,7 @@
         <v>52</v>
       </c>
       <c r="I240" s="19">
-        <v>337</v>
+        <v>307</v>
       </c>
     </row>
     <row r="241" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12672,7 +12672,7 @@
         <v>61</v>
       </c>
       <c r="I241" s="19">
-        <v>427</v>
+        <v>509</v>
       </c>
     </row>
     <row r="242" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12701,7 +12701,7 @@
         <v>52</v>
       </c>
       <c r="I242" s="19">
-        <v>368</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12730,7 +12730,7 @@
         <v>52</v>
       </c>
       <c r="I243" s="19">
-        <v>252</v>
+        <v>203</v>
       </c>
     </row>
     <row r="244" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12759,7 +12759,7 @@
         <v>61</v>
       </c>
       <c r="I244" s="19">
-        <v>147</v>
+        <v>179</v>
       </c>
     </row>
     <row r="245" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12788,7 +12788,7 @@
         <v>52</v>
       </c>
       <c r="I245" s="19">
-        <v>218</v>
+        <v>306</v>
       </c>
     </row>
     <row r="246" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12817,7 +12817,7 @@
         <v>52</v>
       </c>
       <c r="I246" s="19">
-        <v>471</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12846,7 +12846,7 @@
         <v>61</v>
       </c>
       <c r="I247" s="19">
-        <v>345</v>
+        <v>485</v>
       </c>
     </row>
     <row r="248" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12875,7 +12875,7 @@
         <v>52</v>
       </c>
       <c r="I248" s="19">
-        <v>406</v>
+        <v>229</v>
       </c>
     </row>
     <row r="249" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12904,7 +12904,7 @@
         <v>52</v>
       </c>
       <c r="I249" s="19">
-        <v>194</v>
+        <v>469</v>
       </c>
     </row>
     <row r="250" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12933,7 +12933,7 @@
         <v>61</v>
       </c>
       <c r="I250" s="19">
-        <v>329</v>
+        <v>201</v>
       </c>
     </row>
     <row r="251" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12962,7 +12962,7 @@
         <v>52</v>
       </c>
       <c r="I251" s="19">
-        <v>271</v>
+        <v>172</v>
       </c>
     </row>
     <row r="252" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -12991,7 +12991,7 @@
         <v>52</v>
       </c>
       <c r="I252" s="19">
-        <v>443</v>
+        <v>409</v>
       </c>
     </row>
     <row r="253" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13020,7 +13020,7 @@
         <v>61</v>
       </c>
       <c r="I253" s="19">
-        <v>296</v>
+        <v>312</v>
       </c>
     </row>
     <row r="254" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13049,7 +13049,7 @@
         <v>52</v>
       </c>
       <c r="I254" s="19">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="255" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13078,7 +13078,7 @@
         <v>52</v>
       </c>
       <c r="I255" s="19">
-        <v>451</v>
+        <v>288</v>
       </c>
     </row>
     <row r="256" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13107,7 +13107,7 @@
         <v>61</v>
       </c>
       <c r="I256" s="19">
-        <v>479</v>
+        <v>343</v>
       </c>
     </row>
     <row r="257" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13136,7 +13136,7 @@
         <v>52</v>
       </c>
       <c r="I257" s="19">
-        <v>137</v>
+        <v>260</v>
       </c>
     </row>
     <row r="258" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13165,7 +13165,7 @@
         <v>52</v>
       </c>
       <c r="I258" s="19">
-        <v>360</v>
+        <v>243</v>
       </c>
     </row>
     <row r="259" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13194,7 +13194,7 @@
         <v>61</v>
       </c>
       <c r="I259" s="19">
-        <v>482</v>
+        <v>316</v>
       </c>
     </row>
     <row r="260" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13223,7 +13223,7 @@
         <v>52</v>
       </c>
       <c r="I260" s="19">
-        <v>462</v>
+        <v>243</v>
       </c>
     </row>
     <row r="261" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13252,7 +13252,7 @@
         <v>52</v>
       </c>
       <c r="I261" s="19">
-        <v>377</v>
+        <v>279</v>
       </c>
     </row>
     <row r="262" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13281,7 +13281,7 @@
         <v>61</v>
       </c>
       <c r="I262" s="19">
-        <v>351</v>
+        <v>121</v>
       </c>
     </row>
     <row r="263" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13310,7 +13310,7 @@
         <v>52</v>
       </c>
       <c r="I263" s="19">
-        <v>271</v>
+        <v>174</v>
       </c>
     </row>
     <row r="264" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13339,7 +13339,7 @@
         <v>52</v>
       </c>
       <c r="I264" s="19">
-        <v>502</v>
+        <v>175</v>
       </c>
     </row>
     <row r="265" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13368,7 +13368,7 @@
         <v>61</v>
       </c>
       <c r="I265" s="19">
-        <v>507</v>
+        <v>497</v>
       </c>
     </row>
     <row r="266" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13397,7 +13397,7 @@
         <v>52</v>
       </c>
       <c r="I266" s="19">
-        <v>253</v>
+        <v>158</v>
       </c>
     </row>
     <row r="267" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13426,7 +13426,7 @@
         <v>52</v>
       </c>
       <c r="I267" s="19">
-        <v>243</v>
+        <v>127</v>
       </c>
     </row>
     <row r="268" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13455,7 +13455,7 @@
         <v>61</v>
       </c>
       <c r="I268" s="19">
-        <v>263</v>
+        <v>384</v>
       </c>
     </row>
     <row r="269" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13484,7 +13484,7 @@
         <v>52</v>
       </c>
       <c r="I269" s="19">
-        <v>134</v>
+        <v>308</v>
       </c>
     </row>
     <row r="270" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13513,7 +13513,7 @@
         <v>52</v>
       </c>
       <c r="I270" s="19">
-        <v>248</v>
+        <v>368</v>
       </c>
     </row>
     <row r="271" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13542,7 +13542,7 @@
         <v>61</v>
       </c>
       <c r="I271" s="19">
-        <v>124</v>
+        <v>214</v>
       </c>
     </row>
     <row r="272" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13571,7 +13571,7 @@
         <v>52</v>
       </c>
       <c r="I272" s="19">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="273" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13600,7 +13600,7 @@
         <v>52</v>
       </c>
       <c r="I273" s="19">
-        <v>401</v>
+        <v>300</v>
       </c>
     </row>
     <row r="274" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13629,7 +13629,7 @@
         <v>61</v>
       </c>
       <c r="I274" s="19">
-        <v>473</v>
+        <v>439</v>
       </c>
     </row>
     <row r="275" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13658,7 +13658,7 @@
         <v>52</v>
       </c>
       <c r="I275" s="19">
-        <v>457</v>
+        <v>277</v>
       </c>
     </row>
     <row r="276" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13687,7 +13687,7 @@
         <v>273</v>
       </c>
       <c r="I276" s="19">
-        <v>242</v>
+        <v>321</v>
       </c>
     </row>
     <row r="277" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13716,7 +13716,7 @@
         <v>61</v>
       </c>
       <c r="I277" s="19">
-        <v>246</v>
+        <v>313</v>
       </c>
     </row>
     <row r="278" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13745,7 +13745,7 @@
         <v>52</v>
       </c>
       <c r="I278" s="19">
-        <v>146</v>
+        <v>253</v>
       </c>
     </row>
     <row r="279" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13774,7 +13774,7 @@
         <v>52</v>
       </c>
       <c r="I279" s="19">
-        <v>467</v>
+        <v>171</v>
       </c>
     </row>
     <row r="280" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13803,7 +13803,7 @@
         <v>61</v>
       </c>
       <c r="I280" s="19">
-        <v>221</v>
+        <v>493</v>
       </c>
     </row>
     <row r="281" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13832,7 +13832,7 @@
         <v>52</v>
       </c>
       <c r="I281" s="19">
-        <v>260</v>
+        <v>408</v>
       </c>
     </row>
     <row r="282" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13861,7 +13861,7 @@
         <v>52</v>
       </c>
       <c r="I282" s="19">
-        <v>177</v>
+        <v>432</v>
       </c>
     </row>
     <row r="283" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13890,7 +13890,7 @@
         <v>61</v>
       </c>
       <c r="I283" s="19">
-        <v>126</v>
+        <v>267</v>
       </c>
     </row>
     <row r="284" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13919,7 +13919,7 @@
         <v>52</v>
       </c>
       <c r="I284" s="19">
-        <v>368</v>
+        <v>503</v>
       </c>
     </row>
     <row r="285" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13948,7 +13948,7 @@
         <v>52</v>
       </c>
       <c r="I285" s="19">
-        <v>506</v>
+        <v>407</v>
       </c>
     </row>
     <row r="286" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13977,7 +13977,7 @@
         <v>61</v>
       </c>
       <c r="I286" s="19">
-        <v>283</v>
+        <v>316</v>
       </c>
     </row>
     <row r="287" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14006,7 +14006,7 @@
         <v>52</v>
       </c>
       <c r="I287" s="19">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="288" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14035,7 +14035,7 @@
         <v>52</v>
       </c>
       <c r="I288" s="19">
-        <v>439</v>
+        <v>314</v>
       </c>
     </row>
     <row r="289" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14064,7 +14064,7 @@
         <v>61</v>
       </c>
       <c r="I289" s="19">
-        <v>132</v>
+        <v>168</v>
       </c>
     </row>
     <row r="290" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14093,7 +14093,7 @@
         <v>52</v>
       </c>
       <c r="I290" s="19">
-        <v>484</v>
+        <v>146</v>
       </c>
     </row>
     <row r="291" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14122,7 +14122,7 @@
         <v>52</v>
       </c>
       <c r="I291" s="19">
-        <v>484</v>
+        <v>191</v>
       </c>
     </row>
     <row r="292" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14151,7 +14151,7 @@
         <v>61</v>
       </c>
       <c r="I292" s="19">
-        <v>338</v>
+        <v>315</v>
       </c>
     </row>
     <row r="293" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14180,7 +14180,7 @@
         <v>52</v>
       </c>
       <c r="I293" s="19">
-        <v>121</v>
+        <v>369</v>
       </c>
     </row>
     <row r="294" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14209,7 +14209,7 @@
         <v>52</v>
       </c>
       <c r="I294" s="19">
-        <v>159</v>
+        <v>297</v>
       </c>
     </row>
     <row r="295" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14238,7 +14238,7 @@
         <v>61</v>
       </c>
       <c r="I295" s="19">
-        <v>359</v>
+        <v>398</v>
       </c>
     </row>
     <row r="296" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14267,7 +14267,7 @@
         <v>52</v>
       </c>
       <c r="I296" s="19">
-        <v>130</v>
+        <v>467</v>
       </c>
     </row>
     <row r="297" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14296,7 +14296,7 @@
         <v>52</v>
       </c>
       <c r="I297" s="19">
-        <v>350</v>
+        <v>291</v>
       </c>
     </row>
     <row r="298" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14325,7 +14325,7 @@
         <v>61</v>
       </c>
       <c r="I298" s="19">
-        <v>395</v>
+        <v>362</v>
       </c>
     </row>
     <row r="299" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14354,7 +14354,7 @@
         <v>52</v>
       </c>
       <c r="I299" s="19">
-        <v>222</v>
+        <v>498</v>
       </c>
     </row>
     <row r="300" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14383,7 +14383,7 @@
         <v>52</v>
       </c>
       <c r="I300" s="19">
-        <v>294</v>
+        <v>423</v>
       </c>
     </row>
     <row r="301" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14412,7 +14412,7 @@
         <v>61</v>
       </c>
       <c r="I301" s="19">
-        <v>315</v>
+        <v>426</v>
       </c>
     </row>
     <row r="302" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14441,7 +14441,7 @@
         <v>52</v>
       </c>
       <c r="I302" s="19">
-        <v>158</v>
+        <v>396</v>
       </c>
     </row>
     <row r="303" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14470,7 +14470,7 @@
         <v>52</v>
       </c>
       <c r="I303" s="19">
-        <v>445</v>
+        <v>125</v>
       </c>
     </row>
     <row r="304" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14499,7 +14499,7 @@
         <v>61</v>
       </c>
       <c r="I304" s="19">
-        <v>321</v>
+        <v>185</v>
       </c>
     </row>
     <row r="305" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14528,7 +14528,7 @@
         <v>52</v>
       </c>
       <c r="I305" s="19">
-        <v>241</v>
+        <v>130</v>
       </c>
     </row>
     <row r="306" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -14557,7 +14557,7 @@
         <v>52</v>
       </c>
       <c r="I306" s="19">
-        <v>384</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
